--- a/ACCY122/Assessment II Mock/Calculation - North Gong Surfer School.xlsx
+++ b/ACCY122/Assessment II Mock/Calculation - North Gong Surfer School.xlsx
@@ -1,19 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10412"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Assessment II Mock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II Mock/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9D37BC07-1D87-44A4-B1BD-EAB74EDB7A0A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5788F11B-DC8D-454E-B0E7-9F48761C012E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Journal" sheetId="1" r:id="rId1"/>
+    <sheet name="Ledger" sheetId="2" r:id="rId2"/>
+    <sheet name="Trial Balance" sheetId="3" r:id="rId3"/>
+    <sheet name="Income Statement" sheetId="4" r:id="rId4"/>
+    <sheet name="Balance Statement" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="99">
   <si>
     <t>General Journal</t>
   </si>
@@ -129,13 +133,217 @@
   </si>
   <si>
     <t>(took out cash for personal use)</t>
+  </si>
+  <si>
+    <t>a)</t>
+  </si>
+  <si>
+    <t>Insurance Expense</t>
+  </si>
+  <si>
+    <t>(insurance expired)</t>
+  </si>
+  <si>
+    <t>b)</t>
+  </si>
+  <si>
+    <t>Supplies Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Supplies </t>
+  </si>
+  <si>
+    <t>(supplies used up)</t>
+  </si>
+  <si>
+    <t>c)</t>
+  </si>
+  <si>
+    <t>Depreciation Expense - Equip</t>
+  </si>
+  <si>
+    <t>Accum Depreciation Expense - Equip</t>
+  </si>
+  <si>
+    <t>d)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest Expense </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Interest Payable </t>
+  </si>
+  <si>
+    <t>(depreciation on equipment)</t>
+  </si>
+  <si>
+    <t>(1mth interest)</t>
+  </si>
+  <si>
+    <t>Details</t>
+  </si>
+  <si>
+    <t>Balance c/d</t>
+  </si>
+  <si>
+    <t>Balance b/d</t>
+  </si>
+  <si>
+    <t>Bank Account</t>
+  </si>
+  <si>
+    <t>Capital Account</t>
+  </si>
+  <si>
+    <t>Prepaid Insurance Account</t>
+  </si>
+  <si>
+    <t>Supplies Account</t>
+  </si>
+  <si>
+    <t>AP Account</t>
+  </si>
+  <si>
+    <t>AR Account</t>
+  </si>
+  <si>
+    <t>Service Revenue Account</t>
+  </si>
+  <si>
+    <t>Rent Expense Account</t>
+  </si>
+  <si>
+    <t>Drawings Account</t>
+  </si>
+  <si>
+    <t>Insurance Expense Account</t>
+  </si>
+  <si>
+    <t>Supplies Expense Account</t>
+  </si>
+  <si>
+    <t>Interest Expense Account</t>
+  </si>
+  <si>
+    <t>Trial Balance as at 31 July 2022</t>
+  </si>
+  <si>
+    <t>Office Equipment Account</t>
+  </si>
+  <si>
+    <t>Depreciation - Office Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation Account - Office Equipment</t>
+  </si>
+  <si>
+    <t>Accum Depreciation - Office Equipment</t>
+  </si>
+  <si>
+    <t>Short Term Loan Account</t>
+  </si>
+  <si>
+    <t>Interest Expense</t>
+  </si>
+  <si>
+    <t>Depreciation Expense - Office Equip</t>
+  </si>
+  <si>
+    <t>Depreciation Expense Account - Office Equipment</t>
+  </si>
+  <si>
+    <t>Accumulated Depreciation - Office Equip</t>
+  </si>
+  <si>
+    <t>Interest Payable Account</t>
+  </si>
+  <si>
+    <t>Interest Payable</t>
+  </si>
+  <si>
+    <t>Salaries Expense Account</t>
+  </si>
+  <si>
+    <t>Salaries Expense</t>
+  </si>
+  <si>
+    <t>Income Statement</t>
+  </si>
+  <si>
+    <t>for the month ended 31 Aug 2025</t>
+  </si>
+  <si>
+    <t>INCOME</t>
+  </si>
+  <si>
+    <t>EXPENSE</t>
+  </si>
+  <si>
+    <t>Profit</t>
+  </si>
+  <si>
+    <t>Balance Sheet</t>
+  </si>
+  <si>
+    <t>CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t>TOTAL CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t>NON CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t>TOTAL NON-CURRENT ASSETS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESS: Accumulated Depreciation - Office Equipment </t>
+  </si>
+  <si>
+    <t>TOTAL ASSETS</t>
+  </si>
+  <si>
+    <t>TOTAL LIABILITIES</t>
+  </si>
+  <si>
+    <t>NET ASSETS (TA - TL)</t>
+  </si>
+  <si>
+    <t>OWNER'S EQUITY</t>
+  </si>
+  <si>
+    <t>TOTAL OWNER'S EQUITY</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital </t>
+  </si>
+  <si>
+    <t>as at 31 Aug 2022</t>
+  </si>
+  <si>
+    <t>ADD: Profit for the month ended 31 Aug22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LESS: Drawings </t>
+  </si>
+  <si>
+    <t>CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t>NON CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t>TOTAL CURRENT LIABILITIES</t>
+  </si>
+  <si>
+    <t>1mth int = (6% x 2000 )/12 = 10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -159,6 +367,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -168,7 +383,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="11">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -280,12 +495,123 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -296,30 +622,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="16" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -335,6 +643,111 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>518160</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>150706</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>119310</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C2CE0ABC-75D7-F435-7321-2B92A3D83840}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="518160" y="10657840"/>
+          <a:ext cx="7772400" cy="6103551"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>545253</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>71120</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>420793</xdr:colOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>1362</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A1073AC8-3172-41EE-6090-44ED1B140985}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6979920" y="4558453"/>
+          <a:ext cx="6250940" cy="2061633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -601,595 +1014,634 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="B1:L54"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="10" max="10" width="40.85546875" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" customWidth="1"/>
+    <col min="10" max="10" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="1" t="s">
+    <row r="1" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="34" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
-      <c r="F2" s="3"/>
-      <c r="H2" s="1" t="s">
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="36"/>
+      <c r="H2" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="3"/>
-    </row>
-    <row r="3" spans="2:12" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B3" s="5" t="s">
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="36"/>
+    </row>
+    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="5" t="s">
+      <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="L3" s="3" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B4" s="9">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B4" s="5">
         <v>1</v>
       </c>
-      <c r="C4" s="10">
+      <c r="C4" s="6">
         <v>46204</v>
       </c>
-      <c r="D4" s="11" t="s">
+      <c r="D4" t="s">
         <v>7</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E4">
         <v>4800</v>
       </c>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
-      <c r="C5" s="11"/>
-      <c r="D5" s="18" t="s">
+      <c r="F4" s="7"/>
+      <c r="H4" s="16" t="s">
+        <v>31</v>
+      </c>
+      <c r="I4" s="6">
+        <v>46234</v>
+      </c>
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+      <c r="K4">
+        <v>200</v>
+      </c>
+      <c r="L4" s="7"/>
+    </row>
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B5" s="5"/>
+      <c r="D5" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="12">
+      <c r="F5" s="7">
         <v>4800</v>
       </c>
-    </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B6" s="9"/>
-      <c r="C6" s="11"/>
-      <c r="D6" s="13" t="s">
+      <c r="H5" s="16"/>
+      <c r="J5" s="13" t="s">
+        <v>10</v>
+      </c>
+      <c r="L5" s="7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B6" s="5"/>
+      <c r="D6" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="11"/>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B7" s="9"/>
-      <c r="C7" s="11"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="11"/>
-      <c r="F7" s="12"/>
-    </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B8" s="9">
+      <c r="F6" s="7"/>
+      <c r="H6" s="16"/>
+      <c r="J6" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="L6" s="7"/>
+    </row>
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B7" s="5"/>
+      <c r="F7" s="7"/>
+      <c r="H7" s="16"/>
+      <c r="L7" s="7"/>
+    </row>
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B8" s="5">
         <v>2</v>
       </c>
-      <c r="C8" s="10">
+      <c r="C8" s="6">
         <v>46204</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" t="s">
         <v>10</v>
       </c>
-      <c r="E8" s="11">
+      <c r="E8">
         <v>2400</v>
       </c>
-      <c r="F8" s="12"/>
-    </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B9" s="9"/>
-      <c r="C9" s="11"/>
-      <c r="D9" s="18" t="s">
+      <c r="F8" s="7"/>
+      <c r="H8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="I8" s="6">
+        <v>46234</v>
+      </c>
+      <c r="J8" t="s">
+        <v>35</v>
+      </c>
+      <c r="K8">
+        <v>283</v>
+      </c>
+      <c r="L8" s="7"/>
+    </row>
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B9" s="5"/>
+      <c r="D9" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E9" s="11"/>
-      <c r="F9" s="12">
+      <c r="F9" s="7">
         <v>2400</v>
       </c>
-    </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B10" s="9"/>
-      <c r="C10" s="11"/>
-      <c r="D10" s="13" t="s">
+      <c r="H9" s="16"/>
+      <c r="J9" s="13" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="7">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B10" s="5"/>
+      <c r="D10" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="11"/>
-      <c r="F10" s="12"/>
-    </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B11" s="9"/>
-      <c r="C11" s="11"/>
-      <c r="D11" s="11"/>
-      <c r="E11" s="11"/>
-      <c r="F11" s="12"/>
-    </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B12" s="9">
+      <c r="F10" s="7"/>
+      <c r="H10" s="16"/>
+      <c r="J10" s="8" t="s">
+        <v>37</v>
+      </c>
+      <c r="L10" s="7"/>
+    </row>
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B11" s="5"/>
+      <c r="F11" s="7"/>
+      <c r="H11" s="16"/>
+      <c r="L11" s="7"/>
+    </row>
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B12" s="5">
         <v>3</v>
       </c>
-      <c r="C12" s="10">
+      <c r="C12" s="6">
         <v>46210</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" t="s">
         <v>11</v>
       </c>
-      <c r="E12" s="11">
+      <c r="E12">
         <v>600</v>
       </c>
-      <c r="F12" s="12"/>
-    </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B13" s="9"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="18" t="s">
+      <c r="F12" s="7"/>
+      <c r="H12" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="I12" s="6">
+        <v>46234</v>
+      </c>
+      <c r="J12" t="s">
+        <v>39</v>
+      </c>
+      <c r="K12">
+        <v>100</v>
+      </c>
+      <c r="L12" s="7"/>
+    </row>
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B13" s="5"/>
+      <c r="D13" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E13" s="11"/>
-      <c r="F13" s="12">
+      <c r="F13" s="7">
         <v>600</v>
       </c>
-    </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B14" s="9"/>
-      <c r="C14" s="11"/>
-      <c r="D14" s="13" t="s">
+      <c r="H13" s="16"/>
+      <c r="J13" s="13" t="s">
+        <v>40</v>
+      </c>
+      <c r="L13">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B14" s="5"/>
+      <c r="D14" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="11"/>
-      <c r="F14" s="12"/>
-    </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B15" s="9"/>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="12"/>
-    </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B16" s="9">
+      <c r="F14" s="7"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="6"/>
+      <c r="J14" s="8" t="s">
+        <v>44</v>
+      </c>
+      <c r="L14" s="7"/>
+    </row>
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B15" s="5"/>
+      <c r="F15" s="7"/>
+      <c r="H15" s="16"/>
+      <c r="L15" s="7"/>
+    </row>
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B16" s="5">
         <v>4</v>
       </c>
-      <c r="C16" s="10">
+      <c r="C16" s="6">
         <v>46212</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" t="s">
         <v>14</v>
       </c>
-      <c r="E16" s="11">
+      <c r="E16">
         <v>3264</v>
       </c>
-      <c r="F16" s="12"/>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B17" s="9"/>
-      <c r="C17" s="11"/>
-      <c r="D17" s="18" t="s">
+      <c r="F16" s="7"/>
+      <c r="H16" s="16" t="s">
+        <v>41</v>
+      </c>
+      <c r="I16" s="6">
+        <v>46234</v>
+      </c>
+      <c r="J16" t="s">
+        <v>42</v>
+      </c>
+      <c r="K16">
+        <v>10</v>
+      </c>
+      <c r="L16" s="7"/>
+    </row>
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="5"/>
+      <c r="D17" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E17" s="11"/>
-      <c r="F17" s="12">
+      <c r="F17" s="7">
         <v>3264</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B18" s="9"/>
-      <c r="C18" s="11"/>
-      <c r="D18" s="13" t="s">
+      <c r="H17" s="16"/>
+      <c r="J17" s="13" t="s">
+        <v>43</v>
+      </c>
+      <c r="L17" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="5"/>
+      <c r="D18" s="8" t="s">
         <v>15</v>
       </c>
-      <c r="E18" s="11"/>
-      <c r="F18" s="12"/>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B19" s="9"/>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="12"/>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B20" s="9">
+      <c r="F18" s="7"/>
+      <c r="H18" s="16"/>
+      <c r="I18" s="6"/>
+      <c r="J18" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="L18" s="7"/>
+    </row>
+    <row r="19" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B19" s="5"/>
+      <c r="F19" s="7"/>
+      <c r="H19" s="16"/>
+      <c r="K19" s="4">
+        <f>SUM(K4:K18)</f>
+        <v>593</v>
+      </c>
+      <c r="L19" s="9">
+        <f>SUM(L4:L18)</f>
+        <v>593</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="5">
         <v>5</v>
       </c>
-      <c r="C20" s="10">
+      <c r="C20" s="6">
         <v>46213</v>
       </c>
-      <c r="D20" s="11" t="s">
+      <c r="D20" t="s">
         <v>16</v>
       </c>
-      <c r="E20" s="11">
+      <c r="E20">
         <v>1467</v>
       </c>
-      <c r="F20" s="12"/>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B21" s="9"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="18" t="s">
+      <c r="F20" s="7"/>
+      <c r="H20" s="10"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
+      <c r="K20" s="11"/>
+      <c r="L20" s="12"/>
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="5"/>
+      <c r="D21" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E21" s="11"/>
-      <c r="F21" s="12">
+      <c r="F21" s="7">
         <v>1467</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B22" s="9"/>
-      <c r="C22" s="11"/>
-      <c r="D22" s="13" t="s">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="5"/>
+      <c r="D22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="12"/>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B23" s="9"/>
-      <c r="C23" s="11"/>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11"/>
-      <c r="F23" s="12"/>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B24" s="9">
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="5"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="5">
         <v>6</v>
       </c>
-      <c r="C24" s="10">
+      <c r="C24" s="6">
         <v>46217</v>
       </c>
-      <c r="D24" s="11" t="s">
+      <c r="D24" t="s">
         <v>18</v>
       </c>
-      <c r="E24" s="11">
+      <c r="E24">
         <v>6000</v>
       </c>
-      <c r="F24" s="12"/>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B25" s="9"/>
-      <c r="C25" s="11"/>
-      <c r="D25" s="18" t="s">
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="5"/>
+      <c r="D25" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E25" s="11"/>
-      <c r="F25" s="12">
+      <c r="F25" s="7">
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B26" s="9"/>
-      <c r="C26" s="11"/>
-      <c r="D26" s="18" t="s">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B26" s="5"/>
+      <c r="D26" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="E26" s="11"/>
-      <c r="F26" s="12">
+      <c r="F26" s="7">
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B27" s="9"/>
-      <c r="C27" s="11"/>
-      <c r="D27" s="13" t="s">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="5"/>
+      <c r="D27" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="E27" s="11"/>
-      <c r="F27" s="12"/>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B28" s="9"/>
-      <c r="C28" s="10"/>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11"/>
-      <c r="F28" s="12"/>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B29" s="9">
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B28" s="5"/>
+      <c r="C28" s="6"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="5">
         <v>7</v>
       </c>
-      <c r="C29" s="10">
+      <c r="C29" s="6">
         <v>46218</v>
       </c>
-      <c r="D29" s="11" t="s">
+      <c r="D29" t="s">
         <v>7</v>
       </c>
-      <c r="E29" s="11">
+      <c r="E29">
         <v>2000</v>
       </c>
-      <c r="F29" s="12"/>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B30" s="9"/>
-      <c r="C30" s="11"/>
-      <c r="D30" s="18" t="s">
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="5"/>
+      <c r="D30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="11"/>
-      <c r="F30" s="12">
+      <c r="F30" s="7">
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B31" s="9"/>
-      <c r="C31" s="11"/>
-      <c r="D31" s="13" t="s">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="5"/>
+      <c r="D31" s="8" t="s">
         <v>21</v>
       </c>
-      <c r="E31" s="11"/>
-      <c r="F31" s="12"/>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B32" s="9"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="12"/>
-    </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B33" s="9">
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B32" s="5"/>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B33" s="5">
         <v>8</v>
       </c>
-      <c r="C33" s="10">
+      <c r="C33" s="6">
         <v>46220</v>
       </c>
-      <c r="D33" s="11" t="s">
+      <c r="D33" t="s">
         <v>7</v>
       </c>
-      <c r="E33" s="11">
+      <c r="E33">
         <v>3264</v>
       </c>
-      <c r="F33" s="12"/>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B34" s="9"/>
-      <c r="C34" s="11"/>
-      <c r="D34" s="18" t="s">
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B34" s="5"/>
+      <c r="D34" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="E34" s="11"/>
-      <c r="F34" s="12">
+      <c r="F34" s="7">
         <v>3264</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B35" s="9"/>
-      <c r="C35" s="11"/>
-      <c r="D35" s="13" t="s">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B35" s="5"/>
+      <c r="D35" s="8" t="s">
         <v>22</v>
       </c>
-      <c r="E35" s="11"/>
-      <c r="F35" s="12"/>
-    </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B36" s="9"/>
-      <c r="C36" s="11"/>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11"/>
-      <c r="F36" s="12"/>
-    </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B37" s="9">
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B36" s="5"/>
+      <c r="F36" s="7"/>
+      <c r="H36" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B37" s="5">
         <v>9</v>
       </c>
-      <c r="C37" s="10">
+      <c r="C37" s="6">
         <v>46222</v>
       </c>
-      <c r="D37" s="11" t="s">
+      <c r="D37" t="s">
         <v>23</v>
       </c>
-      <c r="E37" s="11">
+      <c r="E37">
         <v>300</v>
       </c>
-      <c r="F37" s="12"/>
-    </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B38" s="9"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="18" t="s">
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B38" s="5"/>
+      <c r="D38" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="12">
+      <c r="F38" s="7">
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B39" s="9"/>
-      <c r="C39" s="11"/>
-      <c r="D39" s="13" t="s">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B39" s="5"/>
+      <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="12"/>
-    </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B40" s="9"/>
-      <c r="C40" s="11"/>
-      <c r="D40" s="11"/>
-      <c r="E40" s="11"/>
-      <c r="F40" s="12"/>
-    </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B41" s="9">
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B40" s="5"/>
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B41" s="5">
         <v>10</v>
       </c>
-      <c r="C41" s="10">
+      <c r="C41" s="6">
         <v>46225</v>
       </c>
-      <c r="D41" s="11" t="s">
+      <c r="D41" t="s">
         <v>7</v>
       </c>
-      <c r="E41" s="11">
+      <c r="E41">
         <v>3536</v>
       </c>
-      <c r="F41" s="12"/>
-    </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B42" s="9"/>
-      <c r="C42" s="11"/>
-      <c r="D42" s="18" t="s">
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B42" s="5"/>
+      <c r="D42" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="E42" s="11"/>
-      <c r="F42" s="12">
+      <c r="F42" s="7">
         <v>3536</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B43" s="9"/>
-      <c r="C43" s="11"/>
-      <c r="D43" s="13" t="s">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B43" s="5"/>
+      <c r="D43" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="E43" s="11"/>
-      <c r="F43" s="12"/>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B44" s="9"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="12"/>
-    </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B45" s="9">
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B44" s="5"/>
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B45" s="5">
         <v>11</v>
       </c>
-      <c r="C45" s="10">
+      <c r="C45" s="6">
         <v>46234</v>
       </c>
-      <c r="D45" s="11" t="s">
+      <c r="D45" t="s">
         <v>27</v>
       </c>
-      <c r="E45" s="11">
+      <c r="E45">
         <v>3000</v>
       </c>
-      <c r="F45" s="12"/>
-    </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B46" s="9"/>
-      <c r="C46" s="11"/>
-      <c r="D46" s="18" t="s">
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B46" s="5"/>
+      <c r="D46" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="12">
+      <c r="F46" s="7">
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B47" s="9"/>
-      <c r="C47" s="11"/>
-      <c r="D47" s="13" t="s">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B47" s="5"/>
+      <c r="D47" s="8" t="s">
         <v>28</v>
       </c>
-      <c r="E47" s="11"/>
-      <c r="F47" s="12"/>
-    </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B48" s="9"/>
-      <c r="C48" s="11"/>
-      <c r="D48" s="11"/>
-      <c r="E48" s="11"/>
-      <c r="F48" s="12"/>
-    </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B49" s="9">
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+      <c r="B48" s="5"/>
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B49" s="5">
         <v>12</v>
       </c>
-      <c r="C49" s="10">
+      <c r="C49" s="6">
         <v>46234</v>
       </c>
-      <c r="D49" s="11" t="s">
+      <c r="D49" t="s">
         <v>29</v>
       </c>
-      <c r="E49" s="11">
+      <c r="E49">
         <v>667</v>
       </c>
-      <c r="F49" s="12"/>
-    </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B50" s="9"/>
-      <c r="C50" s="11"/>
-      <c r="D50" s="18" t="s">
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B50" s="5"/>
+      <c r="D50" s="13" t="s">
         <v>7</v>
       </c>
-      <c r="E50" s="11"/>
-      <c r="F50" s="12">
+      <c r="F50" s="7">
         <v>667</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B51" s="9"/>
-      <c r="C51" s="11"/>
-      <c r="D51" s="13" t="s">
+    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B51" s="5"/>
+      <c r="D51" s="8" t="s">
         <v>30</v>
       </c>
-      <c r="E51" s="11"/>
-      <c r="F51" s="12"/>
-    </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.25">
-      <c r="B52" s="9"/>
-      <c r="C52" s="11"/>
-      <c r="D52" s="11"/>
-      <c r="E52" s="11"/>
-      <c r="F52" s="12"/>
-    </row>
-    <row r="53" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B53" s="9"/>
-      <c r="C53" s="11"/>
-      <c r="D53" s="11"/>
-      <c r="E53" s="7">
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B52" s="5"/>
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B53" s="5"/>
+      <c r="E53" s="4">
         <f>SUM(E4:E52)</f>
         <v>31298</v>
       </c>
-      <c r="F53" s="14">
+      <c r="F53" s="9">
         <f>SUM(F4:F52)</f>
         <v>31298</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B54" s="15"/>
-      <c r="C54" s="16"/>
-      <c r="D54" s="16"/>
-      <c r="E54" s="16"/>
-      <c r="F54" s="17"/>
+    <row r="54" spans="2:6" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B54" s="10"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1197,5 +1649,1777 @@
     <mergeCell ref="H2:L2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63510609-EF1D-6C47-B6EA-5E080B01FD3F}">
+  <dimension ref="B3:N76"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="37" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
+      <c r="G3" s="37" t="s">
+        <v>50</v>
+      </c>
+      <c r="H3" s="37"/>
+      <c r="I3" s="37"/>
+      <c r="J3" s="37"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G4" t="s">
+        <v>3</v>
+      </c>
+      <c r="H4" t="s">
+        <v>46</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J4" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B5" s="18">
+        <v>46204</v>
+      </c>
+      <c r="C5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5">
+        <v>4800</v>
+      </c>
+      <c r="G5" s="18">
+        <v>46204</v>
+      </c>
+      <c r="H5" t="s">
+        <v>7</v>
+      </c>
+      <c r="J5">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B6" s="18">
+        <v>46204</v>
+      </c>
+      <c r="C6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6">
+        <v>2400</v>
+      </c>
+      <c r="G6" s="18">
+        <v>46234</v>
+      </c>
+      <c r="H6" t="s">
+        <v>47</v>
+      </c>
+      <c r="J6">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B7" s="18">
+        <v>46213</v>
+      </c>
+      <c r="C7" t="s">
+        <v>16</v>
+      </c>
+      <c r="E7">
+        <v>1467</v>
+      </c>
+      <c r="G7" s="18">
+        <v>46235</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J7">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B8" s="18">
+        <v>46217</v>
+      </c>
+      <c r="C8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B9" s="18">
+        <v>46218</v>
+      </c>
+      <c r="C9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D9">
+        <v>2000</v>
+      </c>
+      <c r="G9" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="37"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B10" s="18">
+        <v>46220</v>
+      </c>
+      <c r="C10" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10">
+        <v>3264</v>
+      </c>
+      <c r="G10" t="s">
+        <v>3</v>
+      </c>
+      <c r="H10" t="s">
+        <v>46</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B11" s="18">
+        <v>46222</v>
+      </c>
+      <c r="C11" t="s">
+        <v>23</v>
+      </c>
+      <c r="E11">
+        <v>300</v>
+      </c>
+      <c r="G11" s="18">
+        <v>46210</v>
+      </c>
+      <c r="H11" t="s">
+        <v>11</v>
+      </c>
+      <c r="J11">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B12" s="18">
+        <v>46225</v>
+      </c>
+      <c r="C12" t="s">
+        <v>25</v>
+      </c>
+      <c r="D12">
+        <v>3536</v>
+      </c>
+      <c r="G12" s="18">
+        <v>46217</v>
+      </c>
+      <c r="H12" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B13" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C13" t="s">
+        <v>27</v>
+      </c>
+      <c r="E13">
+        <v>3000</v>
+      </c>
+      <c r="G13" s="18">
+        <v>46222</v>
+      </c>
+      <c r="H13" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B14" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C14" t="s">
+        <v>29</v>
+      </c>
+      <c r="E14">
+        <v>667</v>
+      </c>
+      <c r="G14" s="18">
+        <v>46234</v>
+      </c>
+      <c r="H14" t="s">
+        <v>47</v>
+      </c>
+      <c r="I14">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B15" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C15" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="E15">
+        <v>4766</v>
+      </c>
+      <c r="G15" s="14"/>
+      <c r="I15" s="4">
+        <v>5600</v>
+      </c>
+      <c r="J15" s="4">
+        <v>5600</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="14"/>
+      <c r="D16" s="4">
+        <f>SUM(D5:D15)</f>
+        <v>13600</v>
+      </c>
+      <c r="E16" s="4">
+        <f>SUM(E5:E15)</f>
+        <v>13600</v>
+      </c>
+      <c r="G16" s="18">
+        <v>46235</v>
+      </c>
+      <c r="H16" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J16">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B17" s="18">
+        <v>46235</v>
+      </c>
+      <c r="C17" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17">
+        <v>4766</v>
+      </c>
+      <c r="G17" s="18"/>
+    </row>
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="G18" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="H18" s="37"/>
+      <c r="I18" s="37"/>
+      <c r="J18" s="37"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="37" t="s">
+        <v>51</v>
+      </c>
+      <c r="C19" s="37"/>
+      <c r="D19" s="37"/>
+      <c r="E19" s="37"/>
+      <c r="G19" t="s">
+        <v>3</v>
+      </c>
+      <c r="H19" t="s">
+        <v>46</v>
+      </c>
+      <c r="I19" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J19" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B20" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" t="s">
+        <v>46</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G20" s="18">
+        <v>46212</v>
+      </c>
+      <c r="H20" s="15" t="s">
+        <v>14</v>
+      </c>
+      <c r="J20">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B21" s="18">
+        <v>46204</v>
+      </c>
+      <c r="C21" t="s">
+        <v>7</v>
+      </c>
+      <c r="D21">
+        <v>2400</v>
+      </c>
+      <c r="G21" s="18">
+        <v>46225</v>
+      </c>
+      <c r="H21" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="J21">
+        <v>3536</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B22" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C22" t="s">
+        <v>32</v>
+      </c>
+      <c r="E22">
+        <v>200</v>
+      </c>
+      <c r="J22" s="21">
+        <f>SUM(J20:J21)</f>
+        <v>6800</v>
+      </c>
+      <c r="M22" s="1"/>
+      <c r="N22" s="1"/>
+    </row>
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B23" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C23" t="s">
+        <v>47</v>
+      </c>
+      <c r="E23">
+        <v>2200</v>
+      </c>
+      <c r="G23" s="37"/>
+      <c r="H23" s="37"/>
+      <c r="I23" s="37"/>
+      <c r="J23" s="37"/>
+      <c r="K23" s="18"/>
+    </row>
+    <row r="24" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="14"/>
+      <c r="D24" s="4">
+        <v>2400</v>
+      </c>
+      <c r="E24" s="4">
+        <v>2400</v>
+      </c>
+      <c r="G24" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H24" s="37"/>
+      <c r="I24" s="37"/>
+      <c r="J24" s="37"/>
+      <c r="M24" s="1"/>
+      <c r="N24" s="1"/>
+    </row>
+    <row r="25" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B25" s="18">
+        <v>46235</v>
+      </c>
+      <c r="C25" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25">
+        <v>2200</v>
+      </c>
+      <c r="G25" t="s">
+        <v>3</v>
+      </c>
+      <c r="H25" t="s">
+        <v>46</v>
+      </c>
+      <c r="I25" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J25" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K25" s="37"/>
+      <c r="L25" s="37"/>
+      <c r="M25" s="37"/>
+      <c r="N25" s="37"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="G26" s="18">
+        <v>46234</v>
+      </c>
+      <c r="H26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26">
+        <v>667</v>
+      </c>
+      <c r="M26" s="1"/>
+      <c r="N26" s="1"/>
+    </row>
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B27" s="37" t="s">
+        <v>52</v>
+      </c>
+      <c r="C27" s="37"/>
+      <c r="D27" s="37"/>
+      <c r="E27" s="37"/>
+      <c r="G27" s="37"/>
+      <c r="H27" s="37"/>
+      <c r="I27" s="37"/>
+      <c r="J27" s="37"/>
+      <c r="K27" s="18"/>
+      <c r="L27" s="15"/>
+    </row>
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B28" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" t="s">
+        <v>46</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G28" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" s="37"/>
+      <c r="K28" s="18"/>
+    </row>
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B29" s="18">
+        <v>46210</v>
+      </c>
+      <c r="C29" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D29">
+        <v>600</v>
+      </c>
+      <c r="G29" t="s">
+        <v>3</v>
+      </c>
+      <c r="H29" t="s">
+        <v>46</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J29" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K29" s="18"/>
+      <c r="L29" s="19"/>
+    </row>
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B30" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C30" t="s">
+        <v>35</v>
+      </c>
+      <c r="E30">
+        <v>283</v>
+      </c>
+      <c r="G30" s="18">
+        <v>46225</v>
+      </c>
+      <c r="H30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="J30">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B31" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C31" t="s">
+        <v>47</v>
+      </c>
+      <c r="E31">
+        <v>317</v>
+      </c>
+      <c r="G31" s="18">
+        <v>46234</v>
+      </c>
+      <c r="H31" t="s">
+        <v>47</v>
+      </c>
+      <c r="J31">
+        <v>2000</v>
+      </c>
+      <c r="K31" s="37"/>
+      <c r="L31" s="37"/>
+      <c r="M31" s="37"/>
+      <c r="N31" s="37"/>
+    </row>
+    <row r="32" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B32" s="14"/>
+      <c r="D32" s="4">
+        <v>600</v>
+      </c>
+      <c r="E32" s="4">
+        <v>600</v>
+      </c>
+      <c r="G32" s="18">
+        <v>46235</v>
+      </c>
+      <c r="H32" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J32">
+        <v>2000</v>
+      </c>
+      <c r="M32" s="1"/>
+      <c r="N32" s="1"/>
+    </row>
+    <row r="33" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+      <c r="B33" s="18">
+        <v>46235</v>
+      </c>
+      <c r="C33" t="s">
+        <v>48</v>
+      </c>
+      <c r="D33">
+        <v>317</v>
+      </c>
+      <c r="G33" s="37"/>
+      <c r="H33" s="37"/>
+      <c r="I33" s="37"/>
+      <c r="J33" s="37"/>
+      <c r="K33" s="18"/>
+    </row>
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B34" s="18"/>
+      <c r="G34" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="H34" s="37"/>
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="18"/>
+    </row>
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="C35" s="37"/>
+      <c r="D35" s="37"/>
+      <c r="E35" s="37"/>
+      <c r="G35" t="s">
+        <v>3</v>
+      </c>
+      <c r="H35" t="s">
+        <v>46</v>
+      </c>
+      <c r="I35" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="J35" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K35" s="18"/>
+      <c r="L35" s="19"/>
+    </row>
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B36" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D36" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E36" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G36" s="18">
+        <v>46234</v>
+      </c>
+      <c r="H36" t="s">
+        <v>42</v>
+      </c>
+      <c r="J36">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B37" s="18">
+        <v>46217</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="D37">
+        <v>1000</v>
+      </c>
+      <c r="G37" s="18">
+        <v>46234</v>
+      </c>
+      <c r="H37" t="s">
+        <v>47</v>
+      </c>
+      <c r="J37">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B38" s="18">
+        <v>46217</v>
+      </c>
+      <c r="C38" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D38">
+        <v>5000</v>
+      </c>
+      <c r="G38" s="18">
+        <v>46235</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="J38">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B39" s="18"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="21">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B40" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C40" t="s">
+        <v>47</v>
+      </c>
+      <c r="D40">
+        <v>6000</v>
+      </c>
+    </row>
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B41" s="18">
+        <v>46235</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41">
+        <v>6000</v>
+      </c>
+      <c r="G41" s="37"/>
+      <c r="H41" s="37"/>
+      <c r="I41" s="37"/>
+      <c r="J41" s="37"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="I42" s="1"/>
+      <c r="J42" s="1"/>
+    </row>
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43" s="37" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="37"/>
+      <c r="D43" s="37"/>
+      <c r="E43" s="37"/>
+      <c r="G43" s="18"/>
+      <c r="H43" s="15"/>
+    </row>
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B44" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" t="s">
+        <v>46</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E44" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G44" s="18"/>
+      <c r="H44" s="15"/>
+    </row>
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B45" s="18">
+        <v>46212</v>
+      </c>
+      <c r="C45" t="s">
+        <v>25</v>
+      </c>
+      <c r="D45">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B46" s="18">
+        <v>46220</v>
+      </c>
+      <c r="C46" t="s">
+        <v>7</v>
+      </c>
+      <c r="E46">
+        <v>3264</v>
+      </c>
+    </row>
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="I47" s="1"/>
+      <c r="J47" s="1"/>
+    </row>
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="C48" s="37"/>
+      <c r="D48" s="37"/>
+      <c r="E48" s="37"/>
+      <c r="G48" s="18"/>
+    </row>
+    <row r="49" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B49" t="s">
+        <v>3</v>
+      </c>
+      <c r="C49" t="s">
+        <v>46</v>
+      </c>
+      <c r="D49" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E49" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I49" s="1"/>
+      <c r="J49" s="1"/>
+    </row>
+    <row r="50" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B50" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C50" t="s">
+        <v>7</v>
+      </c>
+      <c r="D50">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="51" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="I51" s="1"/>
+      <c r="J51" s="1"/>
+    </row>
+    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B52" s="37" t="s">
+        <v>58</v>
+      </c>
+      <c r="C52" s="37"/>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="G52" s="18"/>
+      <c r="H52" s="15"/>
+    </row>
+    <row r="53" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B53" t="s">
+        <v>3</v>
+      </c>
+      <c r="C53" t="s">
+        <v>46</v>
+      </c>
+      <c r="D53" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E53" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G53" s="18"/>
+    </row>
+    <row r="54" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B54" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C54" t="s">
+        <v>10</v>
+      </c>
+      <c r="D54">
+        <v>200</v>
+      </c>
+      <c r="G54" s="18"/>
+      <c r="H54" s="19"/>
+    </row>
+    <row r="56" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B56" s="37" t="s">
+        <v>59</v>
+      </c>
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B57" t="s">
+        <v>3</v>
+      </c>
+      <c r="C57" t="s">
+        <v>46</v>
+      </c>
+      <c r="D57" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E57" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
+    </row>
+    <row r="58" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B58" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C58" t="s">
+        <v>11</v>
+      </c>
+      <c r="D58">
+        <v>283</v>
+      </c>
+      <c r="G58" s="18"/>
+    </row>
+    <row r="59" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="G59" s="18"/>
+    </row>
+    <row r="60" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B60" s="37" t="s">
+        <v>73</v>
+      </c>
+      <c r="C60" s="37"/>
+      <c r="D60" s="37"/>
+      <c r="E60" s="37"/>
+      <c r="G60" s="18"/>
+    </row>
+    <row r="61" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B61" t="s">
+        <v>3</v>
+      </c>
+      <c r="C61" t="s">
+        <v>46</v>
+      </c>
+      <c r="D61" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E61" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G61" s="18"/>
+    </row>
+    <row r="62" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B62" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="D62">
+        <v>1467</v>
+      </c>
+      <c r="G62" s="18"/>
+    </row>
+    <row r="63" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B63" s="18"/>
+      <c r="G63" s="18"/>
+    </row>
+    <row r="64" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B64" s="37" t="s">
+        <v>60</v>
+      </c>
+      <c r="C64" s="37"/>
+      <c r="D64" s="37"/>
+      <c r="E64" s="37"/>
+      <c r="G64" s="18"/>
+      <c r="H64" s="19"/>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B65" t="s">
+        <v>3</v>
+      </c>
+      <c r="C65" t="s">
+        <v>46</v>
+      </c>
+      <c r="D65" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B66" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C66" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="D66">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B68" s="37" t="s">
+        <v>69</v>
+      </c>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="37"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B69" t="s">
+        <v>3</v>
+      </c>
+      <c r="C69" t="s">
+        <v>46</v>
+      </c>
+      <c r="D69" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B70" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D70">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B72" s="37" t="s">
+        <v>64</v>
+      </c>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="37"/>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B73" t="s">
+        <v>3</v>
+      </c>
+      <c r="C73" t="s">
+        <v>46</v>
+      </c>
+      <c r="D73" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E73" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B74" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C74" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="E74">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B75" s="18">
+        <v>46234</v>
+      </c>
+      <c r="C75" t="s">
+        <v>47</v>
+      </c>
+      <c r="E75">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B76" s="18">
+        <v>46235</v>
+      </c>
+      <c r="C76" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="E76">
+        <v>100</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="24">
+    <mergeCell ref="B35:E35"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="G3:J3"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B27:E27"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="G18:J18"/>
+    <mergeCell ref="G24:J24"/>
+    <mergeCell ref="G23:J23"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B64:E64"/>
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G34:J34"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F27824-797A-F54F-B04B-8F704C481153}">
+  <dimension ref="B1:D22"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="33" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="30"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="20" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>4766</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5">
+        <v>2200</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6">
+        <v>317</v>
+      </c>
+      <c r="D6" s="7"/>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="5" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7">
+        <v>6000</v>
+      </c>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="C8">
+        <v>3000</v>
+      </c>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9">
+        <v>200</v>
+      </c>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10">
+        <v>283</v>
+      </c>
+      <c r="D10" s="7"/>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="C11">
+        <v>1467</v>
+      </c>
+      <c r="D11" s="7"/>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="C12">
+        <v>10</v>
+      </c>
+      <c r="D12" s="7"/>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="C13">
+        <v>100</v>
+      </c>
+      <c r="D13" s="7"/>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="5" t="s">
+        <v>70</v>
+      </c>
+      <c r="D14" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="7">
+        <v>4800</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D16" s="7">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="D17" s="7">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C18">
+        <v>667</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D19" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D20" s="7">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B21" s="5"/>
+      <c r="C21" s="4">
+        <f>SUM(C4:C20)</f>
+        <v>19010</v>
+      </c>
+      <c r="D21" s="9">
+        <f>SUM(D4:D20)</f>
+        <v>19010</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="10"/>
+      <c r="C22" s="11"/>
+      <c r="D22" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3148A8-90AB-1C45-8E98-E96A92823CF0}">
+  <dimension ref="B1:F16"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="31" t="s">
+        <v>76</v>
+      </c>
+      <c r="C3" s="32"/>
+      <c r="D3" s="32"/>
+      <c r="E3" s="32"/>
+      <c r="F3" s="33"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="7">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="5"/>
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="20" t="s">
+        <v>78</v>
+      </c>
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E8">
+        <v>200</v>
+      </c>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E9">
+        <v>283</v>
+      </c>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="5" t="s">
+        <v>74</v>
+      </c>
+      <c r="E10">
+        <v>1467</v>
+      </c>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="E11">
+        <v>10</v>
+      </c>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="E12">
+        <v>3000</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="5" t="s">
+        <v>68</v>
+      </c>
+      <c r="E13">
+        <v>100</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="5"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="23">
+        <f>SUM(E8:E13)</f>
+        <v>5060</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="F15" s="24">
+        <f>F5-F14</f>
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="16" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B16" s="10"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F574CFB-5525-6F48-8029-61180F2430F3}">
+  <dimension ref="B1:F36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="30"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B3" s="31" t="s">
+        <v>92</v>
+      </c>
+      <c r="C3" s="38"/>
+      <c r="D3" s="38"/>
+      <c r="E3" s="38"/>
+      <c r="F3" s="33"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="39"/>
+      <c r="D4" s="39"/>
+      <c r="E4" s="39"/>
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="39"/>
+      <c r="D5" s="39"/>
+      <c r="E5" s="39"/>
+      <c r="F5" s="7">
+        <v>4766</v>
+      </c>
+    </row>
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B6" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="39"/>
+      <c r="F6" s="7">
+        <v>2200</v>
+      </c>
+    </row>
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B7" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="39"/>
+      <c r="E7" s="39"/>
+      <c r="F7" s="7">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B8" s="5"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="39"/>
+      <c r="E8" s="39"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B9" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="C9" s="39"/>
+      <c r="D9" s="39"/>
+      <c r="E9" s="39"/>
+      <c r="F9" s="7">
+        <f>SUM(F5:F8)</f>
+        <v>7283</v>
+      </c>
+    </row>
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B10" s="5"/>
+      <c r="C10" s="39"/>
+      <c r="D10" s="39"/>
+      <c r="E10" s="39"/>
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B11" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="39"/>
+      <c r="E11" s="39"/>
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B12" s="25" t="s">
+        <v>18</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39">
+        <v>6000</v>
+      </c>
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B13" s="25" t="s">
+        <v>85</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="39"/>
+      <c r="E13" s="39">
+        <v>100</v>
+      </c>
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B14" s="25" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="39"/>
+      <c r="D14" s="39"/>
+      <c r="E14" s="39"/>
+      <c r="F14" s="7">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B15" s="5"/>
+      <c r="C15" s="39"/>
+      <c r="D15" s="39"/>
+      <c r="E15" s="39"/>
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B16" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="39"/>
+      <c r="E16" s="39"/>
+      <c r="F16" s="27">
+        <f>SUM(F9+F14)</f>
+        <v>13183</v>
+      </c>
+    </row>
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B17" s="5"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="39"/>
+      <c r="E17" s="39"/>
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B18" s="25" t="s">
+        <v>95</v>
+      </c>
+      <c r="C18" s="39"/>
+      <c r="D18" s="39"/>
+      <c r="E18" s="39"/>
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B19" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="39"/>
+      <c r="E19" s="39"/>
+      <c r="F19" s="7">
+        <v>5300</v>
+      </c>
+    </row>
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B20" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="39"/>
+      <c r="E20" s="39"/>
+      <c r="F20" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B21" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C21" s="39"/>
+      <c r="D21" s="39"/>
+      <c r="E21" s="39"/>
+      <c r="F21" s="7">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B22" s="5" t="s">
+        <v>97</v>
+      </c>
+      <c r="C22" s="39"/>
+      <c r="D22" s="39"/>
+      <c r="E22" s="39"/>
+      <c r="F22" s="7">
+        <f>SUM(F19:F21)</f>
+        <v>7310</v>
+      </c>
+    </row>
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B23" s="25"/>
+      <c r="C23" s="39"/>
+      <c r="D23" s="39"/>
+      <c r="E23" s="39"/>
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B24" s="5"/>
+      <c r="C24" s="39"/>
+      <c r="D24" s="39"/>
+      <c r="E24" s="39"/>
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B25" s="25" t="s">
+        <v>96</v>
+      </c>
+      <c r="C25" s="39"/>
+      <c r="D25" s="39"/>
+      <c r="E25" s="39"/>
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B26" s="25"/>
+      <c r="C26" s="39"/>
+      <c r="D26" s="39"/>
+      <c r="E26" s="39"/>
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B27" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="C27" s="39"/>
+      <c r="D27" s="39"/>
+      <c r="E27" s="39"/>
+      <c r="F27" s="24">
+        <v>7310</v>
+      </c>
+    </row>
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B28" s="5"/>
+      <c r="C28" s="39"/>
+      <c r="D28" s="39"/>
+      <c r="E28" s="39"/>
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B29" s="20" t="s">
+        <v>88</v>
+      </c>
+      <c r="C29" s="39"/>
+      <c r="D29" s="39"/>
+      <c r="E29" s="39"/>
+      <c r="F29" s="24">
+        <f>F16-F27</f>
+        <v>5873</v>
+      </c>
+    </row>
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B30" s="5"/>
+      <c r="C30" s="39"/>
+      <c r="D30" s="39"/>
+      <c r="E30" s="39"/>
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B31" s="5" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="39"/>
+      <c r="D31" s="39"/>
+      <c r="E31" s="39"/>
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B32" s="25" t="s">
+        <v>91</v>
+      </c>
+      <c r="C32" s="39"/>
+      <c r="D32" s="39"/>
+      <c r="E32" s="7">
+        <v>4800</v>
+      </c>
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B33" s="25" t="s">
+        <v>93</v>
+      </c>
+      <c r="C33" s="39"/>
+      <c r="D33" s="39"/>
+      <c r="E33" s="39">
+        <v>1740</v>
+      </c>
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B34" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="39">
+        <v>667</v>
+      </c>
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="B35" s="20" t="s">
+        <v>90</v>
+      </c>
+      <c r="C35" s="39"/>
+      <c r="D35" s="39"/>
+      <c r="E35" s="39"/>
+      <c r="F35" s="24">
+        <v>5873</v>
+      </c>
+    </row>
+    <row r="36" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B36" s="10"/>
+      <c r="C36" s="11"/>
+      <c r="D36" s="11"/>
+      <c r="E36" s="11"/>
+      <c r="F36" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:F2"/>
+    <mergeCell ref="B3:F3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/ACCY122/Assessment II Mock/Calculation - North Gong Surfer School.xlsx
+++ b/ACCY122/Assessment II Mock/Calculation - North Gong Surfer School.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10412"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II Mock/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Assessment II Mock\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5788F11B-DC8D-454E-B0E7-9F48761C012E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CE8E8C-AB5C-4572-A26A-4140FEF04943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="33600" windowHeight="18740" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="105">
   <si>
     <t>General Journal</t>
   </si>
@@ -337,6 +337,24 @@
   </si>
   <si>
     <t>1mth int = (6% x 2000 )/12 = 10</t>
+  </si>
+  <si>
+    <t>deposit = receive money</t>
+  </si>
+  <si>
+    <t>purchase policy = spend money</t>
+  </si>
+  <si>
+    <t>purchase on credit = bill</t>
+  </si>
+  <si>
+    <t>issue invoice = invoice</t>
+  </si>
+  <si>
+    <t>paid wages / expense = spend money</t>
+  </si>
+  <si>
+    <t>short term loan = receive money</t>
   </si>
 </sst>
 </file>
@@ -541,7 +559,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -594,6 +612,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -612,22 +642,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1013,32 +1027,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L54"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B1:L62"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="7" max="7" width="5.1640625" customWidth="1"/>
-    <col min="10" max="10" width="40.83203125" customWidth="1"/>
+    <col min="7" max="7" width="5.140625" customWidth="1"/>
+    <col min="10" max="10" width="40.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="34" t="s">
+    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="B2" s="29" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="35"/>
-      <c r="D2" s="35"/>
-      <c r="E2" s="35"/>
-      <c r="F2" s="36"/>
-      <c r="H2" s="34" t="s">
+      <c r="C2" s="30"/>
+      <c r="D2" s="30"/>
+      <c r="E2" s="30"/>
+      <c r="F2" s="31"/>
+      <c r="H2" s="29" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="35"/>
-      <c r="J2" s="35"/>
-      <c r="K2" s="35"/>
-      <c r="L2" s="36"/>
-    </row>
-    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="I2" s="30"/>
+      <c r="J2" s="30"/>
+      <c r="K2" s="30"/>
+      <c r="L2" s="31"/>
+    </row>
+    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1070,7 +1084,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -1098,7 +1112,7 @@
       </c>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B5" s="5"/>
       <c r="D5" s="13" t="s">
         <v>8</v>
@@ -1114,7 +1128,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
       <c r="D6" s="8" t="s">
         <v>9</v>
@@ -1126,13 +1140,13 @@
       </c>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B7" s="5"/>
       <c r="F7" s="7"/>
       <c r="H7" s="16"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -1160,7 +1174,7 @@
       </c>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B9" s="5"/>
       <c r="D9" s="13" t="s">
         <v>7</v>
@@ -1176,7 +1190,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B10" s="5"/>
       <c r="D10" s="8" t="s">
         <v>12</v>
@@ -1188,13 +1202,13 @@
       </c>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B11" s="5"/>
       <c r="F11" s="7"/>
       <c r="H11" s="16"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B12" s="5">
         <v>3</v>
       </c>
@@ -1222,7 +1236,7 @@
       </c>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B13" s="5"/>
       <c r="D13" s="13" t="s">
         <v>23</v>
@@ -1238,7 +1252,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="D14" s="8" t="s">
         <v>13</v>
@@ -1251,13 +1265,13 @@
       </c>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
       <c r="F15" s="7"/>
       <c r="H15" s="16"/>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B16" s="5">
         <v>4</v>
       </c>
@@ -1285,7 +1299,7 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
       <c r="D17" s="13" t="s">
         <v>25</v>
@@ -1301,7 +1315,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B18" s="5"/>
       <c r="D18" s="8" t="s">
         <v>15</v>
@@ -1314,7 +1328,7 @@
       </c>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B19" s="5"/>
       <c r="F19" s="7"/>
       <c r="H19" s="16"/>
@@ -1327,7 +1341,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="5">
         <v>5</v>
       </c>
@@ -1347,7 +1361,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="D21" s="13" t="s">
         <v>7</v>
@@ -1356,18 +1370,18 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B22" s="5"/>
       <c r="D22" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B23" s="5"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B24" s="5">
         <v>6</v>
       </c>
@@ -1382,7 +1396,7 @@
       </c>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B25" s="5"/>
       <c r="D25" s="13" t="s">
         <v>7</v>
@@ -1391,7 +1405,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B26" s="5"/>
       <c r="D26" s="13" t="s">
         <v>23</v>
@@ -1400,19 +1414,19 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B27" s="5"/>
       <c r="D27" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
       <c r="C28" s="6"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B29" s="5">
         <v>7</v>
       </c>
@@ -1427,7 +1441,7 @@
       </c>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1436,18 +1450,18 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B31" s="5"/>
       <c r="D31" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B32" s="5"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B33" s="5">
         <v>8</v>
       </c>
@@ -1462,7 +1476,7 @@
       </c>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B34" s="5"/>
       <c r="D34" s="13" t="s">
         <v>14</v>
@@ -1471,21 +1485,21 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B35" s="5"/>
       <c r="D35" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B36" s="5"/>
       <c r="F36" s="7"/>
       <c r="H36" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B37" s="5">
         <v>9</v>
       </c>
@@ -1500,7 +1514,7 @@
       </c>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B38" s="5"/>
       <c r="D38" s="13" t="s">
         <v>7</v>
@@ -1509,18 +1523,18 @@
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B39" s="5"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B40" s="5"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B41" s="5">
         <v>10</v>
       </c>
@@ -1535,7 +1549,7 @@
       </c>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B42" s="5"/>
       <c r="D42" s="13" t="s">
         <v>25</v>
@@ -1544,18 +1558,18 @@
         <v>3536</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B43" s="5"/>
       <c r="D43" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B44" s="5"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B45" s="5">
         <v>11</v>
       </c>
@@ -1570,7 +1584,7 @@
       </c>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B46" s="5"/>
       <c r="D46" s="13" t="s">
         <v>7</v>
@@ -1579,18 +1593,18 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B47" s="5"/>
       <c r="D47" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B48" s="5"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B49" s="5">
         <v>12</v>
       </c>
@@ -1605,7 +1619,7 @@
       </c>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B50" s="5"/>
       <c r="D50" s="13" t="s">
         <v>7</v>
@@ -1614,18 +1628,18 @@
         <v>667</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B51" s="5"/>
       <c r="D51" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
       <c r="B52" s="5"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B53" s="5"/>
       <c r="E53" s="4">
         <f>SUM(E4:E52)</f>
@@ -1636,12 +1650,42 @@
         <v>31298</v>
       </c>
     </row>
-    <row r="54" spans="2:6" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
       <c r="F54" s="12"/>
+    </row>
+    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K57" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K58" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K59" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K60" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K61" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="K62" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -1656,29 +1700,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63510609-EF1D-6C47-B6EA-5E080B01FD3F}">
   <dimension ref="B3:N76"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="8.83203125" customWidth="1"/>
-    <col min="3" max="3" width="28.6640625" customWidth="1"/>
-    <col min="6" max="6" width="5.33203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="1" max="1" width="8.85546875" customWidth="1"/>
+    <col min="3" max="3" width="28.7109375" customWidth="1"/>
+    <col min="6" max="6" width="5.28515625" customWidth="1"/>
+    <col min="8" max="8" width="18.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B3" s="37" t="s">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B3" s="28" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
-      <c r="G3" s="37" t="s">
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="28"/>
+      <c r="G3" s="28" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="37"/>
-      <c r="I3" s="37"/>
-      <c r="J3" s="37"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H3" s="28"/>
+      <c r="I3" s="28"/>
+      <c r="J3" s="28"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -1704,7 +1748,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="18">
         <v>46204</v>
       </c>
@@ -1724,7 +1768,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B6" s="18">
         <v>46204</v>
       </c>
@@ -1744,7 +1788,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="18">
         <v>46213</v>
       </c>
@@ -1764,7 +1808,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B8" s="18">
         <v>46217</v>
       </c>
@@ -1775,7 +1819,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="18">
         <v>46218</v>
       </c>
@@ -1785,14 +1829,14 @@
       <c r="D9">
         <v>2000</v>
       </c>
-      <c r="G9" s="37" t="s">
+      <c r="G9" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="37"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="H9" s="28"/>
+      <c r="I9" s="28"/>
+      <c r="J9" s="28"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B10" s="18">
         <v>46220</v>
       </c>
@@ -1815,7 +1859,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="18">
         <v>46222</v>
       </c>
@@ -1835,7 +1879,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B12" s="18">
         <v>46225</v>
       </c>
@@ -1855,7 +1899,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="18">
         <v>46234</v>
       </c>
@@ -1875,7 +1919,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B14" s="18">
         <v>46234</v>
       </c>
@@ -1895,7 +1939,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B15" s="18">
         <v>46234</v>
       </c>
@@ -1913,7 +1957,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="14"/>
       <c r="D16" s="4">
         <f>SUM(D5:D15)</f>
@@ -1933,7 +1977,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B17" s="18">
         <v>46235</v>
       </c>
@@ -1945,21 +1989,21 @@
       </c>
       <c r="G17" s="18"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="G18" s="37" t="s">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="G18" s="28" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="37"/>
-      <c r="I18" s="37"/>
-      <c r="J18" s="37"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B19" s="37" t="s">
+      <c r="H18" s="28"/>
+      <c r="I18" s="28"/>
+      <c r="J18" s="28"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B19" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="37"/>
-      <c r="D19" s="37"/>
-      <c r="E19" s="37"/>
+      <c r="C19" s="28"/>
+      <c r="D19" s="28"/>
+      <c r="E19" s="28"/>
       <c r="G19" t="s">
         <v>3</v>
       </c>
@@ -1973,7 +2017,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>3</v>
       </c>
@@ -1996,7 +2040,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B21" s="18">
         <v>46204</v>
       </c>
@@ -2016,7 +2060,7 @@
         <v>3536</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B22" s="18">
         <v>46234</v>
       </c>
@@ -2033,7 +2077,7 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B23" s="18">
         <v>46234</v>
       </c>
@@ -2043,13 +2087,13 @@
       <c r="E23">
         <v>2200</v>
       </c>
-      <c r="G23" s="37"/>
-      <c r="H23" s="37"/>
-      <c r="I23" s="37"/>
-      <c r="J23" s="37"/>
+      <c r="G23" s="28"/>
+      <c r="H23" s="28"/>
+      <c r="I23" s="28"/>
+      <c r="J23" s="28"/>
       <c r="K23" s="18"/>
     </row>
-    <row r="24" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B24" s="14"/>
       <c r="D24" s="4">
         <v>2400</v>
@@ -2057,16 +2101,16 @@
       <c r="E24" s="4">
         <v>2400</v>
       </c>
-      <c r="G24" s="37" t="s">
+      <c r="G24" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="37"/>
-      <c r="I24" s="37"/>
-      <c r="J24" s="37"/>
+      <c r="H24" s="28"/>
+      <c r="I24" s="28"/>
+      <c r="J24" s="28"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B25" s="18">
         <v>46235</v>
       </c>
@@ -2088,12 +2132,12 @@
       <c r="J25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K25" s="37"/>
-      <c r="L25" s="37"/>
-      <c r="M25" s="37"/>
-      <c r="N25" s="37"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="K25" s="28"/>
+      <c r="L25" s="28"/>
+      <c r="M25" s="28"/>
+      <c r="N25" s="28"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
       <c r="G26" s="18">
         <v>46234</v>
       </c>
@@ -2106,21 +2150,21 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B27" s="37" t="s">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="B27" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="37"/>
-      <c r="D27" s="37"/>
-      <c r="E27" s="37"/>
-      <c r="G27" s="37"/>
-      <c r="H27" s="37"/>
-      <c r="I27" s="37"/>
-      <c r="J27" s="37"/>
+      <c r="C27" s="28"/>
+      <c r="D27" s="28"/>
+      <c r="E27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="28"/>
+      <c r="J27" s="28"/>
       <c r="K27" s="18"/>
       <c r="L27" s="15"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
         <v>3</v>
       </c>
@@ -2133,15 +2177,15 @@
       <c r="E28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="37" t="s">
+      <c r="G28" s="28" t="s">
         <v>66</v>
       </c>
-      <c r="H28" s="37"/>
-      <c r="I28" s="37"/>
-      <c r="J28" s="37"/>
+      <c r="H28" s="28"/>
+      <c r="I28" s="28"/>
+      <c r="J28" s="28"/>
       <c r="K28" s="18"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B29" s="18">
         <v>46210</v>
       </c>
@@ -2166,7 +2210,7 @@
       <c r="K29" s="18"/>
       <c r="L29" s="19"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B30" s="18">
         <v>46234</v>
       </c>
@@ -2186,7 +2230,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B31" s="18">
         <v>46234</v>
       </c>
@@ -2205,12 +2249,12 @@
       <c r="J31">
         <v>2000</v>
       </c>
-      <c r="K31" s="37"/>
-      <c r="L31" s="37"/>
-      <c r="M31" s="37"/>
-      <c r="N31" s="37"/>
-    </row>
-    <row r="32" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="K31" s="28"/>
+      <c r="L31" s="28"/>
+      <c r="M31" s="28"/>
+      <c r="N31" s="28"/>
+    </row>
+    <row r="32" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B32" s="14"/>
       <c r="D32" s="4">
         <v>600</v>
@@ -2230,7 +2274,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
       <c r="B33" s="18">
         <v>46235</v>
       </c>
@@ -2240,29 +2284,29 @@
       <c r="D33">
         <v>317</v>
       </c>
-      <c r="G33" s="37"/>
-      <c r="H33" s="37"/>
-      <c r="I33" s="37"/>
-      <c r="J33" s="37"/>
+      <c r="G33" s="28"/>
+      <c r="H33" s="28"/>
+      <c r="I33" s="28"/>
+      <c r="J33" s="28"/>
       <c r="K33" s="18"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B34" s="18"/>
-      <c r="G34" s="37" t="s">
+      <c r="G34" s="28" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="37"/>
-      <c r="I34" s="37"/>
-      <c r="J34" s="37"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="28"/>
+      <c r="J34" s="28"/>
       <c r="K34" s="18"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B35" s="37" t="s">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B35" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="37"/>
-      <c r="D35" s="37"/>
-      <c r="E35" s="37"/>
+      <c r="C35" s="28"/>
+      <c r="D35" s="28"/>
+      <c r="E35" s="28"/>
       <c r="G35" t="s">
         <v>3</v>
       </c>
@@ -2278,7 +2322,7 @@
       <c r="K35" s="18"/>
       <c r="L35" s="19"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -2301,7 +2345,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B37" s="18">
         <v>46217</v>
       </c>
@@ -2321,7 +2365,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B38" s="18">
         <v>46217</v>
       </c>
@@ -2338,17 +2382,17 @@
         <v>48</v>
       </c>
       <c r="J38">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
       <c r="D39" s="21">
         <v>6000</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B40" s="18">
         <v>46234</v>
       </c>
@@ -2359,7 +2403,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B41" s="18">
         <v>46235</v>
       </c>
@@ -2369,26 +2413,26 @@
       <c r="D41">
         <v>6000</v>
       </c>
-      <c r="G41" s="37"/>
-      <c r="H41" s="37"/>
-      <c r="I41" s="37"/>
-      <c r="J41" s="37"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="G41" s="28"/>
+      <c r="H41" s="28"/>
+      <c r="I41" s="28"/>
+      <c r="J41" s="28"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B43" s="37" t="s">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B43" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="37"/>
-      <c r="D43" s="37"/>
-      <c r="E43" s="37"/>
+      <c r="C43" s="28"/>
+      <c r="D43" s="28"/>
+      <c r="E43" s="28"/>
       <c r="G43" s="18"/>
       <c r="H43" s="15"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>3</v>
       </c>
@@ -2404,7 +2448,7 @@
       <c r="G44" s="18"/>
       <c r="H44" s="15"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B45" s="18">
         <v>46212</v>
       </c>
@@ -2415,7 +2459,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
       <c r="B46" s="18">
         <v>46220</v>
       </c>
@@ -2426,20 +2470,20 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
-      <c r="B48" s="37" t="s">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="B48" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="37"/>
-      <c r="D48" s="37"/>
-      <c r="E48" s="37"/>
+      <c r="C48" s="28"/>
+      <c r="D48" s="28"/>
+      <c r="E48" s="28"/>
       <c r="G48" s="18"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>3</v>
       </c>
@@ -2455,7 +2499,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="18">
         <v>46234</v>
       </c>
@@ -2466,21 +2510,21 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B52" s="37" t="s">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B52" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="37"/>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
+      <c r="C52" s="28"/>
+      <c r="D52" s="28"/>
+      <c r="E52" s="28"/>
       <c r="G52" s="18"/>
       <c r="H52" s="15"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>3</v>
       </c>
@@ -2495,7 +2539,7 @@
       </c>
       <c r="G53" s="18"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="18">
         <v>46234</v>
       </c>
@@ -2508,15 +2552,15 @@
       <c r="G54" s="18"/>
       <c r="H54" s="19"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B56" s="37" t="s">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B56" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="C56" s="28"/>
+      <c r="D56" s="28"/>
+      <c r="E56" s="28"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -2532,7 +2576,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="18">
         <v>46234</v>
       </c>
@@ -2544,19 +2588,19 @@
       </c>
       <c r="G58" s="18"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="G59" s="18"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B60" s="37" t="s">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B60" s="28" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="37"/>
-      <c r="D60" s="37"/>
-      <c r="E60" s="37"/>
+      <c r="C60" s="28"/>
+      <c r="D60" s="28"/>
+      <c r="E60" s="28"/>
       <c r="G60" s="18"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" t="s">
         <v>3</v>
       </c>
@@ -2571,7 +2615,7 @@
       </c>
       <c r="G61" s="18"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="18">
         <v>46234</v>
       </c>
@@ -2583,21 +2627,21 @@
       </c>
       <c r="G62" s="18"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.2">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="18"/>
       <c r="G63" s="18"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B64" s="37" t="s">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B64" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="37"/>
-      <c r="D64" s="37"/>
-      <c r="E64" s="37"/>
+      <c r="C64" s="28"/>
+      <c r="D64" s="28"/>
+      <c r="E64" s="28"/>
       <c r="G64" s="18"/>
       <c r="H64" s="19"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B65" t="s">
         <v>3</v>
       </c>
@@ -2611,7 +2655,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B66" s="18">
         <v>46234</v>
       </c>
@@ -2622,15 +2666,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B68" s="37" t="s">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B68" s="28" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="37"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C68" s="28"/>
+      <c r="D68" s="28"/>
+      <c r="E68" s="28"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B69" t="s">
         <v>3</v>
       </c>
@@ -2644,7 +2688,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B70" s="18">
         <v>46234</v>
       </c>
@@ -2655,15 +2699,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B72" s="37" t="s">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B72" s="28" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="37"/>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="C72" s="28"/>
+      <c r="D72" s="28"/>
+      <c r="E72" s="28"/>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B73" t="s">
         <v>3</v>
       </c>
@@ -2677,7 +2721,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B74" s="18">
         <v>46234</v>
       </c>
@@ -2688,7 +2732,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B75" s="18">
         <v>46234</v>
       </c>
@@ -2699,7 +2743,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B76" s="18">
         <v>46235</v>
       </c>
@@ -2744,20 +2788,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F27824-797A-F54F-B04B-8F704C481153}">
   <dimension ref="B1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B2" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="30"/>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="C2" s="33"/>
+      <c r="D2" s="34"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B3" s="20" t="s">
         <v>4</v>
       </c>
@@ -2768,7 +2812,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2777,7 +2821,7 @@
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
@@ -2786,7 +2830,7 @@
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
@@ -2795,7 +2839,7 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
@@ -2804,7 +2848,7 @@
       </c>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
@@ -2813,7 +2857,7 @@
       </c>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
@@ -2822,7 +2866,7 @@
       </c>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
@@ -2831,7 +2875,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>74</v>
       </c>
@@ -2840,7 +2884,7 @@
       </c>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>67</v>
       </c>
@@ -2849,7 +2893,7 @@
       </c>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>68</v>
       </c>
@@ -2858,7 +2902,7 @@
       </c>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B14" s="5" t="s">
         <v>70</v>
       </c>
@@ -2866,7 +2910,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2874,7 +2918,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -2882,7 +2926,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
@@ -2890,7 +2934,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B18" s="5" t="s">
         <v>29</v>
       </c>
@@ -2899,7 +2943,7 @@
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>72</v>
       </c>
@@ -2907,7 +2951,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
@@ -2915,7 +2959,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B21" s="5"/>
       <c r="C21" s="4">
         <f>SUM(C4:C20)</f>
@@ -2926,7 +2970,7 @@
         <v>19010</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
@@ -2942,34 +2986,34 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3148A8-90AB-1C45-8E98-E96A92823CF0}">
   <dimension ref="B1:F16"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="32" t="s">
         <v>75</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="31" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="32"/>
-      <c r="D3" s="32"/>
-      <c r="E3" s="32"/>
-      <c r="F3" s="33"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="20" t="s">
         <v>77</v>
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
@@ -2977,17 +3021,17 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="5"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="5" t="s">
         <v>32</v>
       </c>
@@ -2996,7 +3040,7 @@
       </c>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
@@ -3005,7 +3049,7 @@
       </c>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="5" t="s">
         <v>74</v>
       </c>
@@ -3014,7 +3058,7 @@
       </c>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>67</v>
       </c>
@@ -3023,7 +3067,7 @@
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
@@ -3032,7 +3076,7 @@
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="5" t="s">
         <v>68</v>
       </c>
@@ -3041,7 +3085,7 @@
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="5"/>
       <c r="E14" s="22"/>
       <c r="F14" s="23">
@@ -3049,7 +3093,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="20" t="s">
         <v>79</v>
       </c>
@@ -3058,7 +3102,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -3077,338 +3121,247 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F574CFB-5525-6F48-8029-61180F2430F3}">
   <dimension ref="B1:F36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B2" s="28" t="s">
+    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B2" s="32" t="s">
         <v>80</v>
       </c>
-      <c r="C2" s="29"/>
-      <c r="D2" s="29"/>
-      <c r="E2" s="29"/>
-      <c r="F2" s="30"/>
-    </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
-      <c r="B3" s="31" t="s">
+      <c r="C2" s="33"/>
+      <c r="D2" s="33"/>
+      <c r="E2" s="33"/>
+      <c r="F2" s="34"/>
+    </row>
+    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+      <c r="B3" s="35" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="38"/>
-      <c r="D3" s="38"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="33"/>
-    </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
+      <c r="C3" s="36"/>
+      <c r="D3" s="36"/>
+      <c r="E3" s="36"/>
+      <c r="F3" s="37"/>
+    </row>
+    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B4" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="39"/>
-      <c r="D4" s="39"/>
-      <c r="E4" s="39"/>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="39"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="39"/>
       <c r="F5" s="7">
         <v>4766</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="39"/>
-      <c r="D6" s="39"/>
-      <c r="E6" s="39"/>
       <c r="F6" s="7">
         <v>2200</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="39"/>
-      <c r="D7" s="39"/>
-      <c r="E7" s="39"/>
       <c r="F7" s="7">
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B8" s="5"/>
-      <c r="C8" s="39"/>
-      <c r="D8" s="39"/>
-      <c r="E8" s="39"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B9" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="C9" s="39"/>
-      <c r="D9" s="39"/>
-      <c r="E9" s="39"/>
       <c r="F9" s="7">
         <f>SUM(F5:F8)</f>
         <v>7283</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B10" s="5"/>
-      <c r="C10" s="39"/>
-      <c r="D10" s="39"/>
-      <c r="E10" s="39"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B11" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="C11" s="39"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="39"/>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B12" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39">
+      <c r="E12">
         <v>6000</v>
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B13" s="25" t="s">
         <v>85</v>
       </c>
-      <c r="C13" s="39"/>
-      <c r="D13" s="39"/>
-      <c r="E13" s="39">
+      <c r="E13">
         <v>100</v>
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B14" s="25" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="39"/>
-      <c r="D14" s="39"/>
-      <c r="E14" s="39"/>
       <c r="F14" s="7">
         <v>5900</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B15" s="5"/>
-      <c r="C15" s="39"/>
-      <c r="D15" s="39"/>
-      <c r="E15" s="39"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B16" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C16" s="39"/>
-      <c r="D16" s="39"/>
-      <c r="E16" s="39"/>
       <c r="F16" s="27">
         <f>SUM(F9+F14)</f>
         <v>13183</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B17" s="5"/>
-      <c r="C17" s="39"/>
-      <c r="D17" s="39"/>
-      <c r="E17" s="39"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B18" s="25" t="s">
         <v>95</v>
       </c>
-      <c r="C18" s="39"/>
-      <c r="D18" s="39"/>
-      <c r="E18" s="39"/>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="C19" s="39"/>
-      <c r="D19" s="39"/>
-      <c r="E19" s="39"/>
       <c r="F19" s="7">
         <v>5300</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B20" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="C20" s="39"/>
-      <c r="D20" s="39"/>
-      <c r="E20" s="39"/>
       <c r="F20" s="7">
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B21" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="C21" s="39"/>
-      <c r="D21" s="39"/>
-      <c r="E21" s="39"/>
       <c r="F21" s="7">
         <v>2000</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B22" s="5" t="s">
         <v>97</v>
       </c>
-      <c r="C22" s="39"/>
-      <c r="D22" s="39"/>
-      <c r="E22" s="39"/>
       <c r="F22" s="7">
         <f>SUM(F19:F21)</f>
         <v>7310</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B23" s="25"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B24" s="5"/>
-      <c r="C24" s="39"/>
-      <c r="D24" s="39"/>
-      <c r="E24" s="39"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B25" s="25" t="s">
         <v>96</v>
       </c>
-      <c r="C25" s="39"/>
-      <c r="D25" s="39"/>
-      <c r="E25" s="39"/>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B26" s="25"/>
-      <c r="C26" s="39"/>
-      <c r="D26" s="39"/>
-      <c r="E26" s="39"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B27" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="39"/>
-      <c r="D27" s="39"/>
-      <c r="E27" s="39"/>
       <c r="F27" s="24">
         <v>7310</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B28" s="5"/>
-      <c r="C28" s="39"/>
-      <c r="D28" s="39"/>
-      <c r="E28" s="39"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B29" s="20" t="s">
         <v>88</v>
       </c>
-      <c r="C29" s="39"/>
-      <c r="D29" s="39"/>
-      <c r="E29" s="39"/>
       <c r="F29" s="24">
         <f>F16-F27</f>
         <v>5873</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B30" s="5"/>
-      <c r="C30" s="39"/>
-      <c r="D30" s="39"/>
-      <c r="E30" s="39"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B31" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="C31" s="39"/>
-      <c r="D31" s="39"/>
-      <c r="E31" s="39"/>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B32" s="25" t="s">
         <v>91</v>
       </c>
-      <c r="C32" s="39"/>
-      <c r="D32" s="39"/>
       <c r="E32" s="7">
         <v>4800</v>
       </c>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B33" s="25" t="s">
         <v>93</v>
       </c>
-      <c r="C33" s="39"/>
-      <c r="D33" s="39"/>
-      <c r="E33" s="39">
+      <c r="E33">
         <v>1740</v>
       </c>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B34" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C34" s="39"/>
-      <c r="D34" s="39"/>
-      <c r="E34" s="39">
+      <c r="E34">
         <v>667</v>
       </c>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
       <c r="B35" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
       <c r="F35" s="24">
         <v>5873</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>

--- a/ACCY122/Assessment II Mock/Calculation - North Gong Surfer School.xlsx
+++ b/ACCY122/Assessment II Mock/Calculation - North Gong Surfer School.xlsx
@@ -1,23 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10419"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Assessment II Mock\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/joseph/Desktop/SIM-UOW-Mods/ACCY122/Assessment II Mock/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50CE8E8C-AB5C-4572-A26A-4140FEF04943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A29095-7E6B-6D4C-9C02-23F3097B72D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20" yWindow="500" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Journal" sheetId="1" r:id="rId1"/>
     <sheet name="Ledger" sheetId="2" r:id="rId2"/>
-    <sheet name="Trial Balance" sheetId="3" r:id="rId3"/>
-    <sheet name="Income Statement" sheetId="4" r:id="rId4"/>
-    <sheet name="Balance Statement" sheetId="5" r:id="rId5"/>
+    <sheet name="Closing Entry" sheetId="6" r:id="rId3"/>
+    <sheet name="Trial Balance" sheetId="3" r:id="rId4"/>
+    <sheet name="Income Statement" sheetId="4" r:id="rId5"/>
+    <sheet name="Balance Statement" sheetId="5" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="105">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="118">
   <si>
     <t>General Journal</t>
   </si>
@@ -355,6 +356,45 @@
   </si>
   <si>
     <t>short term loan = receive money</t>
+  </si>
+  <si>
+    <t>ref 8 - existing invoice</t>
+  </si>
+  <si>
+    <t>ref 9 - existing invoice</t>
+  </si>
+  <si>
+    <t>ref 10 - receive money</t>
+  </si>
+  <si>
+    <t>ref 11 &amp; 12 - spend money</t>
+  </si>
+  <si>
+    <t>Closing Entries</t>
+  </si>
+  <si>
+    <t>DR ($)</t>
+  </si>
+  <si>
+    <t>CR ($)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Service Revenue </t>
+  </si>
+  <si>
+    <t>Profit &amp; Loss Summary</t>
+  </si>
+  <si>
+    <t>(Close Revenue Account)</t>
+  </si>
+  <si>
+    <t>(Close Expense Account)</t>
+  </si>
+  <si>
+    <t>(Xfer P/L to Capital)</t>
+  </si>
+  <si>
+    <t>(Close drawings account)</t>
   </si>
 </sst>
 </file>
@@ -559,7 +599,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="48">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -612,9 +652,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -623,6 +660,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -640,6 +680,30 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -1027,32 +1091,32 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B1:L62"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="B1:L66"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="4" max="4" width="40" customWidth="1"/>
-    <col min="7" max="7" width="5.140625" customWidth="1"/>
-    <col min="10" max="10" width="40.85546875" customWidth="1"/>
+    <col min="7" max="7" width="5.1640625" customWidth="1"/>
+    <col min="10" max="10" width="40.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="29" t="s">
+    <row r="1" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="B2" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="30"/>
-      <c r="D2" s="30"/>
-      <c r="E2" s="30"/>
-      <c r="F2" s="31"/>
-      <c r="H2" s="29" t="s">
+      <c r="C2" s="29"/>
+      <c r="D2" s="29"/>
+      <c r="E2" s="29"/>
+      <c r="F2" s="30"/>
+      <c r="H2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="I2" s="30"/>
-      <c r="J2" s="30"/>
-      <c r="K2" s="30"/>
-      <c r="L2" s="31"/>
-    </row>
-    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="I2" s="29"/>
+      <c r="J2" s="29"/>
+      <c r="K2" s="29"/>
+      <c r="L2" s="30"/>
+    </row>
+    <row r="3" spans="2:12" s="1" customFormat="1" x14ac:dyDescent="0.2">
       <c r="B3" s="2" t="s">
         <v>2</v>
       </c>
@@ -1084,7 +1148,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B4" s="5">
         <v>1</v>
       </c>
@@ -1112,7 +1176,7 @@
       </c>
       <c r="L4" s="7"/>
     </row>
-    <row r="5" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B5" s="5"/>
       <c r="D5" s="13" t="s">
         <v>8</v>
@@ -1128,7 +1192,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="6" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
       <c r="D6" s="8" t="s">
         <v>9</v>
@@ -1140,13 +1204,13 @@
       </c>
       <c r="L6" s="7"/>
     </row>
-    <row r="7" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B7" s="5"/>
       <c r="F7" s="7"/>
       <c r="H7" s="16"/>
       <c r="L7" s="7"/>
     </row>
-    <row r="8" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B8" s="5">
         <v>2</v>
       </c>
@@ -1174,7 +1238,7 @@
       </c>
       <c r="L8" s="7"/>
     </row>
-    <row r="9" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B9" s="5"/>
       <c r="D9" s="13" t="s">
         <v>7</v>
@@ -1190,7 +1254,7 @@
         <v>283</v>
       </c>
     </row>
-    <row r="10" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B10" s="5"/>
       <c r="D10" s="8" t="s">
         <v>12</v>
@@ -1202,13 +1266,13 @@
       </c>
       <c r="L10" s="7"/>
     </row>
-    <row r="11" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B11" s="5"/>
       <c r="F11" s="7"/>
       <c r="H11" s="16"/>
       <c r="L11" s="7"/>
     </row>
-    <row r="12" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B12" s="5">
         <v>3</v>
       </c>
@@ -1236,7 +1300,7 @@
       </c>
       <c r="L12" s="7"/>
     </row>
-    <row r="13" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B13" s="5"/>
       <c r="D13" s="13" t="s">
         <v>23</v>
@@ -1252,7 +1316,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B14" s="5"/>
       <c r="D14" s="8" t="s">
         <v>13</v>
@@ -1265,13 +1329,13 @@
       </c>
       <c r="L14" s="7"/>
     </row>
-    <row r="15" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B15" s="5"/>
       <c r="F15" s="7"/>
       <c r="H15" s="16"/>
       <c r="L15" s="7"/>
     </row>
-    <row r="16" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B16" s="5">
         <v>4</v>
       </c>
@@ -1299,7 +1363,7 @@
       </c>
       <c r="L16" s="7"/>
     </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B17" s="5"/>
       <c r="D17" s="13" t="s">
         <v>25</v>
@@ -1315,7 +1379,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B18" s="5"/>
       <c r="D18" s="8" t="s">
         <v>15</v>
@@ -1328,7 +1392,7 @@
       </c>
       <c r="L18" s="7"/>
     </row>
-    <row r="19" spans="2:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:12" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B19" s="5"/>
       <c r="F19" s="7"/>
       <c r="H19" s="16"/>
@@ -1341,7 +1405,7 @@
         <v>593</v>
       </c>
     </row>
-    <row r="20" spans="2:12" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:12" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B20" s="5">
         <v>5</v>
       </c>
@@ -1361,7 +1425,7 @@
       <c r="K20" s="11"/>
       <c r="L20" s="12"/>
     </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B21" s="5"/>
       <c r="D21" s="13" t="s">
         <v>7</v>
@@ -1370,18 +1434,18 @@
         <v>1467</v>
       </c>
     </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B22" s="5"/>
       <c r="D22" s="8" t="s">
         <v>17</v>
       </c>
       <c r="F22" s="7"/>
     </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B23" s="5"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B24" s="5">
         <v>6</v>
       </c>
@@ -1396,7 +1460,7 @@
       </c>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B25" s="5"/>
       <c r="D25" s="13" t="s">
         <v>7</v>
@@ -1405,7 +1469,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="26" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B26" s="5"/>
       <c r="D26" s="13" t="s">
         <v>23</v>
@@ -1414,19 +1478,19 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="27" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B27" s="5"/>
       <c r="D27" s="8" t="s">
         <v>19</v>
       </c>
       <c r="F27" s="7"/>
     </row>
-    <row r="28" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B28" s="5"/>
       <c r="C28" s="6"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B29" s="5">
         <v>7</v>
       </c>
@@ -1441,7 +1505,7 @@
       </c>
       <c r="F29" s="7"/>
     </row>
-    <row r="30" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B30" s="5"/>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1450,18 +1514,18 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B31" s="5"/>
       <c r="D31" s="8" t="s">
         <v>21</v>
       </c>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B32" s="5"/>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B33" s="5">
         <v>8</v>
       </c>
@@ -1476,7 +1540,7 @@
       </c>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B34" s="5"/>
       <c r="D34" s="13" t="s">
         <v>14</v>
@@ -1485,21 +1549,21 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B35" s="5"/>
       <c r="D35" s="8" t="s">
         <v>22</v>
       </c>
       <c r="F35" s="7"/>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B36" s="5"/>
       <c r="F36" s="7"/>
       <c r="H36" s="17" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B37" s="5">
         <v>9</v>
       </c>
@@ -1514,7 +1578,7 @@
       </c>
       <c r="F37" s="7"/>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B38" s="5"/>
       <c r="D38" s="13" t="s">
         <v>7</v>
@@ -1523,18 +1587,18 @@
         <v>300</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B39" s="5"/>
       <c r="D39" s="8" t="s">
         <v>24</v>
       </c>
       <c r="F39" s="7"/>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B40" s="5"/>
       <c r="F40" s="7"/>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B41" s="5">
         <v>10</v>
       </c>
@@ -1549,7 +1613,7 @@
       </c>
       <c r="F41" s="7"/>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B42" s="5"/>
       <c r="D42" s="13" t="s">
         <v>25</v>
@@ -1558,18 +1622,18 @@
         <v>3536</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B43" s="5"/>
       <c r="D43" s="8" t="s">
         <v>26</v>
       </c>
       <c r="F43" s="7"/>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B44" s="5"/>
       <c r="F44" s="7"/>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B45" s="5">
         <v>11</v>
       </c>
@@ -1584,7 +1648,7 @@
       </c>
       <c r="F45" s="7"/>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B46" s="5"/>
       <c r="D46" s="13" t="s">
         <v>7</v>
@@ -1593,18 +1657,18 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B47" s="5"/>
       <c r="D47" s="8" t="s">
         <v>28</v>
       </c>
       <c r="F47" s="7"/>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.2">
       <c r="B48" s="5"/>
       <c r="F48" s="7"/>
     </row>
-    <row r="49" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B49" s="5">
         <v>12</v>
       </c>
@@ -1619,7 +1683,7 @@
       </c>
       <c r="F49" s="7"/>
     </row>
-    <row r="50" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B50" s="5"/>
       <c r="D50" s="13" t="s">
         <v>7</v>
@@ -1628,18 +1692,18 @@
         <v>667</v>
       </c>
     </row>
-    <row r="51" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B51" s="5"/>
       <c r="D51" s="8" t="s">
         <v>30</v>
       </c>
       <c r="F51" s="7"/>
     </row>
-    <row r="52" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:11" x14ac:dyDescent="0.2">
       <c r="B52" s="5"/>
       <c r="F52" s="7"/>
     </row>
-    <row r="53" spans="2:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:11" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B53" s="5"/>
       <c r="E53" s="4">
         <f>SUM(E4:E52)</f>
@@ -1650,41 +1714,61 @@
         <v>31298</v>
       </c>
     </row>
-    <row r="54" spans="2:11" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="2:11" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B54" s="10"/>
       <c r="C54" s="11"/>
       <c r="D54" s="11"/>
       <c r="E54" s="11"/>
       <c r="F54" s="12"/>
     </row>
-    <row r="57" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:11" x14ac:dyDescent="0.2">
       <c r="K57" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="58" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:11" x14ac:dyDescent="0.2">
       <c r="K58" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="59" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:11" x14ac:dyDescent="0.2">
       <c r="K59" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="60" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:11" x14ac:dyDescent="0.2">
       <c r="K60" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="61" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:11" x14ac:dyDescent="0.2">
       <c r="K61" t="s">
         <v>103</v>
       </c>
     </row>
-    <row r="62" spans="2:11" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:11" x14ac:dyDescent="0.2">
       <c r="K62" t="s">
         <v>104</v>
+      </c>
+    </row>
+    <row r="63" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K63" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="64" spans="2:11" x14ac:dyDescent="0.2">
+      <c r="K64" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="65" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K65" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="66" spans="11:11" x14ac:dyDescent="0.2">
+      <c r="K66" t="s">
+        <v>108</v>
       </c>
     </row>
   </sheetData>
@@ -1700,29 +1784,29 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63510609-EF1D-6C47-B6EA-5E080B01FD3F}">
   <dimension ref="B3:N76"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="8.85546875" customWidth="1"/>
-    <col min="3" max="3" width="28.7109375" customWidth="1"/>
-    <col min="6" max="6" width="5.28515625" customWidth="1"/>
-    <col min="8" max="8" width="18.85546875" customWidth="1"/>
+    <col min="1" max="1" width="8.83203125" customWidth="1"/>
+    <col min="3" max="3" width="28.6640625" customWidth="1"/>
+    <col min="6" max="6" width="5.33203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B3" s="28" t="s">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B3" s="31" t="s">
         <v>49</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="28"/>
-      <c r="G3" s="28" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="G3" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="H3" s="28"/>
-      <c r="I3" s="28"/>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H3" s="31"/>
+      <c r="I3" s="31"/>
+      <c r="J3" s="31"/>
+    </row>
+    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B4" t="s">
         <v>3</v>
       </c>
@@ -1748,7 +1832,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B5" s="18">
         <v>46204</v>
       </c>
@@ -1768,7 +1852,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B6" s="18">
         <v>46204</v>
       </c>
@@ -1788,7 +1872,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B7" s="18">
         <v>46213</v>
       </c>
@@ -1808,7 +1892,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B8" s="18">
         <v>46217</v>
       </c>
@@ -1819,7 +1903,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B9" s="18">
         <v>46218</v>
       </c>
@@ -1829,14 +1913,14 @@
       <c r="D9">
         <v>2000</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="H9" s="28"/>
-      <c r="I9" s="28"/>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="H9" s="31"/>
+      <c r="I9" s="31"/>
+      <c r="J9" s="31"/>
+    </row>
+    <row r="10" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B10" s="18">
         <v>46220</v>
       </c>
@@ -1859,7 +1943,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B11" s="18">
         <v>46222</v>
       </c>
@@ -1879,7 +1963,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B12" s="18">
         <v>46225</v>
       </c>
@@ -1899,7 +1983,7 @@
         <v>5000</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B13" s="18">
         <v>46234</v>
       </c>
@@ -1919,7 +2003,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="14" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B14" s="18">
         <v>46234</v>
       </c>
@@ -1939,7 +2023,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="15" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="2:10" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B15" s="18">
         <v>46234</v>
       </c>
@@ -1957,7 +2041,7 @@
         <v>5600</v>
       </c>
     </row>
-    <row r="16" spans="2:10" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:10" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="14"/>
       <c r="D16" s="4">
         <f>SUM(D5:D15)</f>
@@ -1977,7 +2061,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="17" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B17" s="18">
         <v>46235</v>
       </c>
@@ -1989,21 +2073,21 @@
       </c>
       <c r="G17" s="18"/>
     </row>
-    <row r="18" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="G18" s="28" t="s">
+    <row r="18" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="G18" s="31" t="s">
         <v>55</v>
       </c>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
-    </row>
-    <row r="19" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B19" s="28" t="s">
+      <c r="H18" s="31"/>
+      <c r="I18" s="31"/>
+      <c r="J18" s="31"/>
+    </row>
+    <row r="19" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B19" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
+      <c r="C19" s="31"/>
+      <c r="D19" s="31"/>
+      <c r="E19" s="31"/>
       <c r="G19" t="s">
         <v>3</v>
       </c>
@@ -2017,7 +2101,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
         <v>3</v>
       </c>
@@ -2040,7 +2124,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="21" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B21" s="18">
         <v>46204</v>
       </c>
@@ -2060,7 +2144,7 @@
         <v>3536</v>
       </c>
     </row>
-    <row r="22" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B22" s="18">
         <v>46234</v>
       </c>
@@ -2077,7 +2161,7 @@
       <c r="M22" s="1"/>
       <c r="N22" s="1"/>
     </row>
-    <row r="23" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B23" s="18">
         <v>46234</v>
       </c>
@@ -2087,13 +2171,13 @@
       <c r="E23">
         <v>2200</v>
       </c>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
       <c r="K23" s="18"/>
     </row>
-    <row r="24" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B24" s="14"/>
       <c r="D24" s="4">
         <v>2400</v>
@@ -2101,16 +2185,16 @@
       <c r="E24" s="4">
         <v>2400</v>
       </c>
-      <c r="G24" s="28" t="s">
+      <c r="G24" s="31" t="s">
         <v>57</v>
       </c>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
+      <c r="H24" s="31"/>
+      <c r="I24" s="31"/>
+      <c r="J24" s="31"/>
       <c r="M24" s="1"/>
       <c r="N24" s="1"/>
     </row>
-    <row r="25" spans="2:14" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:14" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B25" s="18">
         <v>46235</v>
       </c>
@@ -2132,12 +2216,12 @@
       <c r="J25" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="K25" s="28"/>
-      <c r="L25" s="28"/>
-      <c r="M25" s="28"/>
-      <c r="N25" s="28"/>
-    </row>
-    <row r="26" spans="2:14" x14ac:dyDescent="0.25">
+      <c r="K25" s="31"/>
+      <c r="L25" s="31"/>
+      <c r="M25" s="31"/>
+      <c r="N25" s="31"/>
+    </row>
+    <row r="26" spans="2:14" x14ac:dyDescent="0.2">
       <c r="G26" s="18">
         <v>46234</v>
       </c>
@@ -2150,21 +2234,21 @@
       <c r="M26" s="1"/>
       <c r="N26" s="1"/>
     </row>
-    <row r="27" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="B27" s="28" t="s">
+    <row r="27" spans="2:14" x14ac:dyDescent="0.2">
+      <c r="B27" s="31" t="s">
         <v>52</v>
       </c>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="C27" s="31"/>
+      <c r="D27" s="31"/>
+      <c r="E27" s="31"/>
+      <c r="G27" s="31"/>
+      <c r="H27" s="31"/>
+      <c r="I27" s="31"/>
+      <c r="J27" s="31"/>
       <c r="K27" s="18"/>
       <c r="L27" s="15"/>
     </row>
-    <row r="28" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B28" t="s">
         <v>3</v>
       </c>
@@ -2177,15 +2261,15 @@
       <c r="E28" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G28" s="28" t="s">
+      <c r="G28" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="H28" s="31"/>
+      <c r="I28" s="31"/>
+      <c r="J28" s="31"/>
       <c r="K28" s="18"/>
     </row>
-    <row r="29" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B29" s="18">
         <v>46210</v>
       </c>
@@ -2210,7 +2294,7 @@
       <c r="K29" s="18"/>
       <c r="L29" s="19"/>
     </row>
-    <row r="30" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B30" s="18">
         <v>46234</v>
       </c>
@@ -2230,7 +2314,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="31" spans="2:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:14" x14ac:dyDescent="0.2">
       <c r="B31" s="18">
         <v>46234</v>
       </c>
@@ -2249,12 +2333,12 @@
       <c r="J31">
         <v>2000</v>
       </c>
-      <c r="K31" s="28"/>
-      <c r="L31" s="28"/>
-      <c r="M31" s="28"/>
-      <c r="N31" s="28"/>
-    </row>
-    <row r="32" spans="2:14" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="K31" s="31"/>
+      <c r="L31" s="31"/>
+      <c r="M31" s="31"/>
+      <c r="N31" s="31"/>
+    </row>
+    <row r="32" spans="2:14" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B32" s="14"/>
       <c r="D32" s="4">
         <v>600</v>
@@ -2274,7 +2358,7 @@
       <c r="M32" s="1"/>
       <c r="N32" s="1"/>
     </row>
-    <row r="33" spans="2:12" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:12" ht="16" thickTop="1" x14ac:dyDescent="0.2">
       <c r="B33" s="18">
         <v>46235</v>
       </c>
@@ -2284,29 +2368,29 @@
       <c r="D33">
         <v>317</v>
       </c>
-      <c r="G33" s="28"/>
-      <c r="H33" s="28"/>
-      <c r="I33" s="28"/>
-      <c r="J33" s="28"/>
+      <c r="G33" s="31"/>
+      <c r="H33" s="31"/>
+      <c r="I33" s="31"/>
+      <c r="J33" s="31"/>
       <c r="K33" s="18"/>
     </row>
-    <row r="34" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B34" s="18"/>
-      <c r="G34" s="28" t="s">
+      <c r="G34" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="H34" s="28"/>
-      <c r="I34" s="28"/>
-      <c r="J34" s="28"/>
+      <c r="H34" s="31"/>
+      <c r="I34" s="31"/>
+      <c r="J34" s="31"/>
       <c r="K34" s="18"/>
     </row>
-    <row r="35" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B35" s="28" t="s">
+    <row r="35" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B35" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
+      <c r="C35" s="31"/>
+      <c r="D35" s="31"/>
+      <c r="E35" s="31"/>
       <c r="G35" t="s">
         <v>3</v>
       </c>
@@ -2322,7 +2406,7 @@
       <c r="K35" s="18"/>
       <c r="L35" s="19"/>
     </row>
-    <row r="36" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B36" t="s">
         <v>3</v>
       </c>
@@ -2345,7 +2429,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B37" s="18">
         <v>46217</v>
       </c>
@@ -2365,7 +2449,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B38" s="18">
         <v>46217</v>
       </c>
@@ -2385,14 +2469,14 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B39" s="18"/>
       <c r="C39" s="13"/>
       <c r="D39" s="21">
         <v>6000</v>
       </c>
     </row>
-    <row r="40" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B40" s="18">
         <v>46234</v>
       </c>
@@ -2403,7 +2487,7 @@
         <v>6000</v>
       </c>
     </row>
-    <row r="41" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B41" s="18">
         <v>46235</v>
       </c>
@@ -2413,26 +2497,26 @@
       <c r="D41">
         <v>6000</v>
       </c>
-      <c r="G41" s="28"/>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
-    </row>
-    <row r="42" spans="2:12" x14ac:dyDescent="0.25">
+      <c r="G41" s="31"/>
+      <c r="H41" s="31"/>
+      <c r="I41" s="31"/>
+      <c r="J41" s="31"/>
+    </row>
+    <row r="42" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I42" s="1"/>
       <c r="J42" s="1"/>
     </row>
-    <row r="43" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B43" s="28" t="s">
+    <row r="43" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B43" s="31" t="s">
         <v>54</v>
       </c>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
       <c r="G43" s="18"/>
       <c r="H43" s="15"/>
     </row>
-    <row r="44" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B44" t="s">
         <v>3</v>
       </c>
@@ -2448,7 +2532,7 @@
       <c r="G44" s="18"/>
       <c r="H44" s="15"/>
     </row>
-    <row r="45" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B45" s="18">
         <v>46212</v>
       </c>
@@ -2459,7 +2543,7 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="46" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:12" x14ac:dyDescent="0.2">
       <c r="B46" s="18">
         <v>46220</v>
       </c>
@@ -2470,20 +2554,20 @@
         <v>3264</v>
       </c>
     </row>
-    <row r="47" spans="2:12" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:12" x14ac:dyDescent="0.2">
       <c r="I47" s="1"/>
       <c r="J47" s="1"/>
     </row>
-    <row r="48" spans="2:12" x14ac:dyDescent="0.25">
-      <c r="B48" s="28" t="s">
+    <row r="48" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B48" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="C48" s="28"/>
-      <c r="D48" s="28"/>
-      <c r="E48" s="28"/>
+      <c r="C48" s="31"/>
+      <c r="D48" s="31"/>
+      <c r="E48" s="31"/>
       <c r="G48" s="18"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
         <v>3</v>
       </c>
@@ -2499,7 +2583,7 @@
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B50" s="18">
         <v>46234</v>
       </c>
@@ -2510,21 +2594,21 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.2">
       <c r="I51" s="1"/>
       <c r="J51" s="1"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B52" s="28" t="s">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B52" s="31" t="s">
         <v>58</v>
       </c>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
       <c r="G52" s="18"/>
       <c r="H52" s="15"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B53" t="s">
         <v>3</v>
       </c>
@@ -2539,7 +2623,7 @@
       </c>
       <c r="G53" s="18"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B54" s="18">
         <v>46234</v>
       </c>
@@ -2552,15 +2636,15 @@
       <c r="G54" s="18"/>
       <c r="H54" s="19"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B56" s="28" t="s">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B56" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="C56" s="28"/>
-      <c r="D56" s="28"/>
-      <c r="E56" s="28"/>
-    </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="C56" s="31"/>
+      <c r="D56" s="31"/>
+      <c r="E56" s="31"/>
+    </row>
+    <row r="57" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B57" t="s">
         <v>3</v>
       </c>
@@ -2576,7 +2660,7 @@
       <c r="I57" s="1"/>
       <c r="J57" s="1"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B58" s="18">
         <v>46234</v>
       </c>
@@ -2588,19 +2672,19 @@
       </c>
       <c r="G58" s="18"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.2">
       <c r="G59" s="18"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B60" s="28" t="s">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B60" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C60" s="28"/>
-      <c r="D60" s="28"/>
-      <c r="E60" s="28"/>
+      <c r="C60" s="31"/>
+      <c r="D60" s="31"/>
+      <c r="E60" s="31"/>
       <c r="G60" s="18"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B61" t="s">
         <v>3</v>
       </c>
@@ -2615,7 +2699,7 @@
       </c>
       <c r="G61" s="18"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B62" s="18">
         <v>46234</v>
       </c>
@@ -2627,21 +2711,21 @@
       </c>
       <c r="G62" s="18"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.2">
       <c r="B63" s="18"/>
       <c r="G63" s="18"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B64" s="28" t="s">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.2">
+      <c r="B64" s="31" t="s">
         <v>60</v>
       </c>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
       <c r="G64" s="18"/>
       <c r="H64" s="19"/>
     </row>
-    <row r="65" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B65" t="s">
         <v>3</v>
       </c>
@@ -2655,7 +2739,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="66" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B66" s="18">
         <v>46234</v>
       </c>
@@ -2666,15 +2750,15 @@
         <v>10</v>
       </c>
     </row>
-    <row r="68" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B68" s="28" t="s">
+    <row r="68" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B68" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="C68" s="28"/>
-      <c r="D68" s="28"/>
-      <c r="E68" s="28"/>
-    </row>
-    <row r="69" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C68" s="31"/>
+      <c r="D68" s="31"/>
+      <c r="E68" s="31"/>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B69" t="s">
         <v>3</v>
       </c>
@@ -2688,7 +2772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B70" s="18">
         <v>46234</v>
       </c>
@@ -2699,15 +2783,15 @@
         <v>100</v>
       </c>
     </row>
-    <row r="72" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B72" s="28" t="s">
+    <row r="72" spans="2:5" x14ac:dyDescent="0.2">
+      <c r="B72" s="31" t="s">
         <v>64</v>
       </c>
-      <c r="C72" s="28"/>
-      <c r="D72" s="28"/>
-      <c r="E72" s="28"/>
-    </row>
-    <row r="73" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="C72" s="31"/>
+      <c r="D72" s="31"/>
+      <c r="E72" s="31"/>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B73" t="s">
         <v>3</v>
       </c>
@@ -2721,7 +2805,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="74" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B74" s="18">
         <v>46234</v>
       </c>
@@ -2732,7 +2816,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="75" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B75" s="18">
         <v>46234</v>
       </c>
@@ -2743,7 +2827,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="76" spans="2:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B76" s="18">
         <v>46235</v>
       </c>
@@ -2756,6 +2840,20 @@
     </row>
   </sheetData>
   <mergeCells count="24">
+    <mergeCell ref="K25:N25"/>
+    <mergeCell ref="K31:N31"/>
+    <mergeCell ref="G27:J27"/>
+    <mergeCell ref="G33:J33"/>
+    <mergeCell ref="G41:J41"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="G34:J34"/>
+    <mergeCell ref="B60:E60"/>
+    <mergeCell ref="B68:E68"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="B48:E48"/>
+    <mergeCell ref="B52:E52"/>
+    <mergeCell ref="B56:E56"/>
+    <mergeCell ref="B64:E64"/>
     <mergeCell ref="B35:E35"/>
     <mergeCell ref="B43:E43"/>
     <mergeCell ref="B3:E3"/>
@@ -2766,42 +2864,231 @@
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="G23:J23"/>
-    <mergeCell ref="B60:E60"/>
-    <mergeCell ref="B68:E68"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="B48:E48"/>
-    <mergeCell ref="B52:E52"/>
-    <mergeCell ref="B56:E56"/>
-    <mergeCell ref="B64:E64"/>
-    <mergeCell ref="K25:N25"/>
-    <mergeCell ref="K31:N31"/>
-    <mergeCell ref="G27:J27"/>
-    <mergeCell ref="G33:J33"/>
-    <mergeCell ref="G41:J41"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="G34:J34"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2780FFF5-219B-684D-920D-B22B85EE4923}">
+  <dimension ref="B1:D24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="19.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B2" s="42" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="43"/>
+      <c r="D2" s="44"/>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B3" s="45" t="s">
+        <v>109</v>
+      </c>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+    </row>
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="39" t="s">
+        <v>110</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B5" s="5" t="s">
+        <v>112</v>
+      </c>
+      <c r="C5" s="39">
+        <v>6800</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B6" s="38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C6" s="39"/>
+      <c r="D6" s="7">
+        <v>6800</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B7" s="40" t="s">
+        <v>114</v>
+      </c>
+      <c r="C7" s="39"/>
+      <c r="D7" s="7"/>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B8" s="5"/>
+      <c r="C8" s="39"/>
+      <c r="D8" s="7"/>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B9" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C9" s="39">
+        <v>5060</v>
+      </c>
+      <c r="D9" s="7"/>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B10" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="39"/>
+      <c r="D10" s="7">
+        <v>3000</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B11" s="38" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11" s="39"/>
+      <c r="D11" s="7">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B12" s="38" t="s">
+        <v>35</v>
+      </c>
+      <c r="C12" s="39"/>
+      <c r="D12" s="7">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B13" s="38" t="s">
+        <v>74</v>
+      </c>
+      <c r="C13" s="39"/>
+      <c r="D13" s="7">
+        <v>1467</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B14" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="C14" s="39"/>
+      <c r="D14" s="7">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B15" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C15" s="39"/>
+      <c r="D15" s="7">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B16" s="40" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="39"/>
+      <c r="D16" s="7"/>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B17" s="5"/>
+      <c r="C17" s="39"/>
+      <c r="D17" s="7"/>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B18" s="5" t="s">
+        <v>113</v>
+      </c>
+      <c r="C18" s="39">
+        <v>1740</v>
+      </c>
+      <c r="D18" s="7"/>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B19" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="39"/>
+      <c r="D19" s="7">
+        <v>1740</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B20" s="40" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" s="39"/>
+      <c r="D20" s="7"/>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B21" s="5"/>
+      <c r="C21" s="39"/>
+      <c r="D21" s="7"/>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B22" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="39">
+        <v>667</v>
+      </c>
+      <c r="D22" s="7"/>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.2">
+      <c r="B23" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C23" s="39"/>
+      <c r="D23" s="7">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B24" s="41" t="s">
+        <v>117</v>
+      </c>
+      <c r="C24" s="11"/>
+      <c r="D24" s="12"/>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B3:D3"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F27824-797A-F54F-B04B-8F704C481153}">
   <dimension ref="B1:D22"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B2" s="32" t="s">
         <v>61</v>
       </c>
       <c r="C2" s="33"/>
       <c r="D2" s="34"/>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B3" s="20" t="s">
         <v>4</v>
       </c>
@@ -2812,7 +3099,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
         <v>7</v>
       </c>
@@ -2821,7 +3108,7 @@
       </c>
       <c r="D4" s="7"/>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>10</v>
       </c>
@@ -2830,7 +3117,7 @@
       </c>
       <c r="D5" s="7"/>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
@@ -2839,7 +3126,7 @@
       </c>
       <c r="D6" s="7"/>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>18</v>
       </c>
@@ -2848,7 +3135,7 @@
       </c>
       <c r="D7" s="7"/>
     </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>27</v>
       </c>
@@ -2857,7 +3144,7 @@
       </c>
       <c r="D8" s="7"/>
     </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>32</v>
       </c>
@@ -2866,7 +3153,7 @@
       </c>
       <c r="D9" s="7"/>
     </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>35</v>
       </c>
@@ -2875,7 +3162,7 @@
       </c>
       <c r="D10" s="7"/>
     </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>74</v>
       </c>
@@ -2884,7 +3171,7 @@
       </c>
       <c r="D11" s="7"/>
     </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
         <v>67</v>
       </c>
@@ -2893,7 +3180,7 @@
       </c>
       <c r="D12" s="7"/>
     </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>68</v>
       </c>
@@ -2902,7 +3189,7 @@
       </c>
       <c r="D13" s="7"/>
     </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B14" s="5" t="s">
         <v>70</v>
       </c>
@@ -2910,7 +3197,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
@@ -2918,7 +3205,7 @@
         <v>4800</v>
       </c>
     </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B16" s="5" t="s">
         <v>23</v>
       </c>
@@ -2926,7 +3213,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B17" s="5" t="s">
         <v>25</v>
       </c>
@@ -2934,7 +3221,7 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B18" s="5" t="s">
         <v>29</v>
       </c>
@@ -2943,7 +3230,7 @@
       </c>
       <c r="D18" s="7"/>
     </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>72</v>
       </c>
@@ -2951,7 +3238,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
         <v>20</v>
       </c>
@@ -2959,7 +3246,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="21" spans="2:4" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:4" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B21" s="5"/>
       <c r="C21" s="4">
         <f>SUM(C4:C20)</f>
@@ -2970,7 +3257,7 @@
         <v>19010</v>
       </c>
     </row>
-    <row r="22" spans="2:4" ht="16.5" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:4" ht="17" thickTop="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B22" s="10"/>
       <c r="C22" s="11"/>
       <c r="D22" s="12"/>
@@ -2983,13 +3270,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0B3148A8-90AB-1C45-8E98-E96A92823CF0}">
   <dimension ref="B1:F16"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="32" t="s">
         <v>75</v>
       </c>
@@ -2998,7 +3285,7 @@
       <c r="E2" s="33"/>
       <c r="F2" s="34"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="35" t="s">
         <v>76</v>
       </c>
@@ -3007,13 +3294,13 @@
       <c r="E3" s="36"/>
       <c r="F3" s="37"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="20" t="s">
         <v>77</v>
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>25</v>
       </c>
@@ -3021,17 +3308,17 @@
         <v>6800</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="5"/>
       <c r="F6" s="7"/>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="20" t="s">
         <v>78</v>
       </c>
       <c r="F7" s="7"/>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="5" t="s">
         <v>32</v>
       </c>
@@ -3040,7 +3327,7 @@
       </c>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>35</v>
       </c>
@@ -3049,7 +3336,7 @@
       </c>
       <c r="F9" s="7"/>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="5" t="s">
         <v>74</v>
       </c>
@@ -3058,7 +3345,7 @@
       </c>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>67</v>
       </c>
@@ -3067,7 +3354,7 @@
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="5" t="s">
         <v>27</v>
       </c>
@@ -3076,7 +3363,7 @@
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="5" t="s">
         <v>68</v>
       </c>
@@ -3085,7 +3372,7 @@
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="5"/>
       <c r="E14" s="22"/>
       <c r="F14" s="23">
@@ -3093,7 +3380,7 @@
         <v>5060</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="20" t="s">
         <v>79</v>
       </c>
@@ -3102,7 +3389,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="16" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B16" s="10"/>
       <c r="C16" s="11"/>
       <c r="D16" s="11"/>
@@ -3118,13 +3405,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F574CFB-5525-6F48-8029-61180F2430F3}">
   <dimension ref="B1:F36"/>
-  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="11.5" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="2" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="2" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B2" s="32" t="s">
         <v>80</v>
       </c>
@@ -3133,7 +3420,7 @@
       <c r="E2" s="33"/>
       <c r="F2" s="34"/>
     </row>
-    <row r="3" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B3" s="35" t="s">
         <v>92</v>
       </c>
@@ -3142,13 +3429,13 @@
       <c r="E3" s="36"/>
       <c r="F3" s="37"/>
     </row>
-    <row r="4" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B4" s="5" t="s">
         <v>81</v>
       </c>
       <c r="F4" s="7"/>
     </row>
-    <row r="5" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B5" s="5" t="s">
         <v>7</v>
       </c>
@@ -3156,7 +3443,7 @@
         <v>4766</v>
       </c>
     </row>
-    <row r="6" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B6" s="5" t="s">
         <v>10</v>
       </c>
@@ -3164,7 +3451,7 @@
         <v>2200</v>
       </c>
     </row>
-    <row r="7" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B7" s="5" t="s">
         <v>11</v>
       </c>
@@ -3172,11 +3459,11 @@
         <v>317</v>
       </c>
     </row>
-    <row r="8" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B8" s="5"/>
       <c r="F8" s="7"/>
     </row>
-    <row r="9" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B9" s="5" t="s">
         <v>82</v>
       </c>
@@ -3185,17 +3472,17 @@
         <v>7283</v>
       </c>
     </row>
-    <row r="10" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B10" s="5"/>
       <c r="F10" s="7"/>
     </row>
-    <row r="11" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B11" s="5" t="s">
         <v>83</v>
       </c>
       <c r="F11" s="7"/>
     </row>
-    <row r="12" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B12" s="25" t="s">
         <v>18</v>
       </c>
@@ -3204,7 +3491,7 @@
       </c>
       <c r="F12" s="7"/>
     </row>
-    <row r="13" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B13" s="25" t="s">
         <v>85</v>
       </c>
@@ -3213,7 +3500,7 @@
       </c>
       <c r="F13" s="7"/>
     </row>
-    <row r="14" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B14" s="25" t="s">
         <v>84</v>
       </c>
@@ -3221,11 +3508,11 @@
         <v>5900</v>
       </c>
     </row>
-    <row r="15" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B15" s="5"/>
       <c r="F15" s="7"/>
     </row>
-    <row r="16" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B16" s="26" t="s">
         <v>86</v>
       </c>
@@ -3234,17 +3521,17 @@
         <v>13183</v>
       </c>
     </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B17" s="5"/>
       <c r="F17" s="7"/>
     </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B18" s="25" t="s">
         <v>95</v>
       </c>
       <c r="F18" s="7"/>
     </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>23</v>
       </c>
@@ -3252,7 +3539,7 @@
         <v>5300</v>
       </c>
     </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
         <v>72</v>
       </c>
@@ -3260,7 +3547,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
         <v>20</v>
       </c>
@@ -3268,7 +3555,7 @@
         <v>2000</v>
       </c>
     </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
         <v>97</v>
       </c>
@@ -3277,25 +3564,25 @@
         <v>7310</v>
       </c>
     </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B23" s="25"/>
       <c r="F23" s="7"/>
     </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B24" s="5"/>
       <c r="F24" s="7"/>
     </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B25" s="25" t="s">
         <v>96</v>
       </c>
       <c r="F25" s="7"/>
     </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B26" s="25"/>
       <c r="F26" s="7"/>
     </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B27" s="26" t="s">
         <v>87</v>
       </c>
@@ -3303,11 +3590,11 @@
         <v>7310</v>
       </c>
     </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B28" s="5"/>
       <c r="F28" s="7"/>
     </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B29" s="20" t="s">
         <v>88</v>
       </c>
@@ -3316,17 +3603,17 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B30" s="5"/>
       <c r="F30" s="7"/>
     </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B31" s="5" t="s">
         <v>89</v>
       </c>
       <c r="F31" s="7"/>
     </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B32" s="25" t="s">
         <v>91</v>
       </c>
@@ -3335,7 +3622,7 @@
       </c>
       <c r="F32" s="7"/>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B33" s="25" t="s">
         <v>93</v>
       </c>
@@ -3344,7 +3631,7 @@
       </c>
       <c r="F33" s="7"/>
     </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B34" s="5" t="s">
         <v>94</v>
       </c>
@@ -3353,7 +3640,7 @@
       </c>
       <c r="F34" s="7"/>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:6" x14ac:dyDescent="0.2">
       <c r="B35" s="20" t="s">
         <v>90</v>
       </c>
@@ -3361,7 +3648,7 @@
         <v>5873</v>
       </c>
     </row>
-    <row r="36" spans="2:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:6" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="B36" s="10"/>
       <c r="C36" s="11"/>
       <c r="D36" s="11"/>
